--- a/outputs/compare_tseeded_lump_unrealized_profits.xlsx
+++ b/outputs/compare_tseeded_lump_unrealized_profits.xlsx
@@ -9,7 +9,7 @@
   <sheets>
     <sheet name="Summary" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="All_Results" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="ddstartup_20251111_220719_param" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="ddstartup_20251112_105650_param" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="ddstartup_20251111_232630_param" sheetId="4" state="visible" r:id="rId4"/>
     <sheet name="S_Q1_Best" sheetId="5" state="visible" r:id="rId5"/>
     <sheet name="S_Q1_Median" sheetId="6" state="visible" r:id="rId6"/>
@@ -494,7 +494,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>ddstartup_20251111_220719_parametric_T_seeded</t>
+          <t>ddstartup_20251112_105650_parametric_T_seeded</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -514,16 +514,16 @@
         <v>1</v>
       </c>
       <c r="F2" t="n">
-        <v>808570.2649719634</v>
+        <v>809022.1304266643</v>
       </c>
       <c r="G2" t="n">
-        <v>808570.2649719634</v>
+        <v>809022.1304266643</v>
       </c>
       <c r="H2" t="n">
-        <v>808570.2649719634</v>
+        <v>809022.1304266643</v>
       </c>
       <c r="I2" t="n">
-        <v>808570.2649719634</v>
+        <v>809022.1304266643</v>
       </c>
       <c r="J2" t="n">
         <v>0</v>
@@ -532,7 +532,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>ddstartup_20251111_220719_parametric_T_seeded</t>
+          <t>ddstartup_20251112_105650_parametric_T_seeded</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -552,16 +552,16 @@
         <v>1</v>
       </c>
       <c r="F3" t="n">
-        <v>31800408.7062685</v>
+        <v>31611486.31443005</v>
       </c>
       <c r="G3" t="n">
-        <v>31800408.7062685</v>
+        <v>31611486.31443005</v>
       </c>
       <c r="H3" t="n">
-        <v>31800408.7062685</v>
+        <v>31611486.31443005</v>
       </c>
       <c r="I3" t="n">
-        <v>31800408.7062685</v>
+        <v>31611486.31443005</v>
       </c>
       <c r="J3" t="n">
         <v>0</v>
@@ -570,7 +570,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>ddstartup_20251111_220719_parametric_T_seeded</t>
+          <t>ddstartup_20251112_105650_parametric_T_seeded</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -590,16 +590,16 @@
         <v>1</v>
       </c>
       <c r="F4" t="n">
-        <v>79825114.2050966</v>
+        <v>79461643.09491301</v>
       </c>
       <c r="G4" t="n">
-        <v>79825114.2050966</v>
+        <v>79461643.09491301</v>
       </c>
       <c r="H4" t="n">
-        <v>79825114.2050966</v>
+        <v>79461643.09491301</v>
       </c>
       <c r="I4" t="n">
-        <v>79825114.2050966</v>
+        <v>79461643.09491301</v>
       </c>
       <c r="J4" t="n">
         <v>0</v>
@@ -608,7 +608,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>ddstartup_20251111_220719_parametric_T_seeded</t>
+          <t>ddstartup_20251112_105650_parametric_T_seeded</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -628,16 +628,16 @@
         <v>1</v>
       </c>
       <c r="F5" t="n">
-        <v>160598012.1906099</v>
+        <v>159868873.5705715</v>
       </c>
       <c r="G5" t="n">
-        <v>160598012.1906099</v>
+        <v>159868873.5705715</v>
       </c>
       <c r="H5" t="n">
-        <v>160598012.1906099</v>
+        <v>159868873.5705715</v>
       </c>
       <c r="I5" t="n">
-        <v>160598012.1906099</v>
+        <v>159868873.5705715</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
@@ -646,7 +646,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>ddstartup_20251111_220719_parametric_T_seeded</t>
+          <t>ddstartup_20251112_105650_parametric_T_seeded</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -666,16 +666,16 @@
         <v>1</v>
       </c>
       <c r="F6" t="n">
-        <v>299048870.0379488</v>
+        <v>297938202.7550347</v>
       </c>
       <c r="G6" t="n">
-        <v>299048870.0379488</v>
+        <v>297938202.7550347</v>
       </c>
       <c r="H6" t="n">
-        <v>299048870.0379488</v>
+        <v>297938202.7550347</v>
       </c>
       <c r="I6" t="n">
-        <v>299048870.0379488</v>
+        <v>297938202.7550347</v>
       </c>
       <c r="J6" t="n">
         <v>0</v>
@@ -684,7 +684,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>ddstartup_20251111_220719_parametric_T_seeded</t>
+          <t>ddstartup_20251112_105650_parametric_T_seeded</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -704,16 +704,16 @@
         <v>1</v>
       </c>
       <c r="F7" t="n">
-        <v>553682224.3456022</v>
+        <v>551214166.5130553</v>
       </c>
       <c r="G7" t="n">
-        <v>553682224.3456022</v>
+        <v>551214166.5130553</v>
       </c>
       <c r="H7" t="n">
-        <v>553682224.3456022</v>
+        <v>551214166.5130553</v>
       </c>
       <c r="I7" t="n">
-        <v>553682224.3456022</v>
+        <v>551214166.5130553</v>
       </c>
       <c r="J7" t="n">
         <v>0</v>
@@ -722,7 +722,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>ddstartup_20251111_220719_parametric_T_seeded</t>
+          <t>ddstartup_20251112_105650_parametric_T_seeded</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -742,16 +742,16 @@
         <v>1</v>
       </c>
       <c r="F8" t="n">
-        <v>1083526000.78126</v>
+        <v>1079477438.890187</v>
       </c>
       <c r="G8" t="n">
-        <v>1083526000.78126</v>
+        <v>1079477438.890187</v>
       </c>
       <c r="H8" t="n">
-        <v>1083526000.78126</v>
+        <v>1079477438.890187</v>
       </c>
       <c r="I8" t="n">
-        <v>1083526000.78126</v>
+        <v>1079477438.890187</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
@@ -760,7 +760,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>ddstartup_20251111_220719_parametric_T_seeded</t>
+          <t>ddstartup_20251112_105650_parametric_T_seeded</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -780,16 +780,16 @@
         <v>1</v>
       </c>
       <c r="F9" t="n">
-        <v>2599566395.617924</v>
+        <v>2593373205.080279</v>
       </c>
       <c r="G9" t="n">
-        <v>2599566395.617924</v>
+        <v>2593373205.080279</v>
       </c>
       <c r="H9" t="n">
-        <v>2599566395.617924</v>
+        <v>2593373205.080279</v>
       </c>
       <c r="I9" t="n">
-        <v>2599566395.617924</v>
+        <v>2593373205.080279</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
@@ -1266,35 +1266,39 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>ddstartup_20251111_220719_parametric_T_seeded</t>
+          <t>ddstartup_20251112_105650_parametric_T_seeded</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>7973024030576672</v>
+        <v>4960927498617498</v>
       </c>
       <c r="E2" t="inlineStr"/>
       <c r="F2" t="n">
-        <v>320348101.1941811</v>
-      </c>
-      <c r="G2" t="inlineStr"/>
-      <c r="H2" t="inlineStr"/>
+        <v>2990807817.052288</v>
+      </c>
+      <c r="G2" t="n">
+        <v>775938308.8975326</v>
+      </c>
+      <c r="H2" t="n">
+        <v>775938308.8975326</v>
+      </c>
       <c r="I2" t="n">
-        <v>0.1602146580159418</v>
+        <v>1.718276282484998</v>
       </c>
       <c r="J2" t="n">
-        <v>0.3541017240527546</v>
+        <v>3.854440208399663</v>
       </c>
       <c r="K2" t="n">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="L2" t="n">
         <v>1.3</v>
       </c>
       <c r="M2" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="N2" t="n">
-        <v>100</v>
+        <v>2000</v>
       </c>
       <c r="O2" t="n">
         <v>0.5</v>
@@ -1308,33 +1312,33 @@
         <v>0.3</v>
       </c>
       <c r="R2" t="n">
-        <v>12943</v>
+        <v>196796</v>
       </c>
       <c r="S2" t="inlineStr"/>
       <c r="T2" t="n">
-        <v>2e+20</v>
+        <v>7e+19</v>
       </c>
       <c r="U2" t="n">
-        <v>6.944444444444444e-08</v>
+        <v>1.111111111111111e-07</v>
       </c>
       <c r="V2" t="b">
         <v>1</v>
       </c>
       <c r="W2" t="n">
-        <v>303032258.2776924</v>
+        <v>19953075.7051578</v>
       </c>
       <c r="X2" t="n">
         <v>43200</v>
       </c>
       <c r="Y2" t="n">
-        <v>86400</v>
+        <v>43200</v>
       </c>
       <c r="Z2" t="inlineStr"/>
       <c r="AA2" t="n">
-        <v>0.1</v>
+        <v>1</v>
       </c>
       <c r="AB2" t="n">
-        <v>553682224.3456022</v>
+        <v>551214166.5130553</v>
       </c>
     </row>
     <row r="3">
@@ -1592,23 +1596,27 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>ddstartup_20251111_220719_parametric_T_seeded</t>
+          <t>ddstartup_20251112_105650_parametric_T_seeded</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>3.900693602812538e+16</v>
+        <v>1.55444751200187e+16</v>
       </c>
       <c r="E2" t="inlineStr"/>
       <c r="F2" t="n">
-        <v>2172581493.312933</v>
-      </c>
-      <c r="G2" t="inlineStr"/>
-      <c r="H2" t="inlineStr"/>
+        <v>3862367099.222991</v>
+      </c>
+      <c r="G2" t="n">
+        <v>717522276.7529577</v>
+      </c>
+      <c r="H2" t="n">
+        <v>717522276.7529577</v>
+      </c>
       <c r="I2" t="n">
-        <v>0.2512639821194254</v>
+        <v>2.950840798869634</v>
       </c>
       <c r="J2" t="n">
-        <v>0.4345284519303243</v>
+        <v>5.38292290617313</v>
       </c>
       <c r="K2" t="n">
         <v>0.5</v>
@@ -1623,7 +1631,7 @@
         <v>500</v>
       </c>
       <c r="O2" t="n">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
       <c r="P2" t="inlineStr">
         <is>
@@ -1634,20 +1642,20 @@
         <v>0.4</v>
       </c>
       <c r="R2" t="n">
-        <v>75861</v>
+        <v>83155</v>
       </c>
       <c r="S2" t="inlineStr"/>
       <c r="T2" t="n">
-        <v>1.5e+20</v>
+        <v>2e+20</v>
       </c>
       <c r="U2" t="n">
-        <v>2.777777777777778e-08</v>
+        <v>6.944444444444444e-08</v>
       </c>
       <c r="V2" t="b">
         <v>1</v>
       </c>
       <c r="W2" t="n">
-        <v>212851007.5009588</v>
+        <v>31812984.14464649</v>
       </c>
       <c r="X2" t="n">
         <v>14400</v>
@@ -1657,10 +1665,10 @@
       </c>
       <c r="Z2" t="inlineStr"/>
       <c r="AA2" t="n">
-        <v>0.1</v>
+        <v>0.5</v>
       </c>
       <c r="AB2" t="n">
-        <v>1083526000.78126</v>
+        <v>1079477438.890187</v>
       </c>
     </row>
     <row r="3">
@@ -1916,38 +1924,42 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>ddstartup_20251111_220719_parametric_T_seeded</t>
+          <t>ddstartup_20251112_105650_parametric_T_seeded</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>2.339609756056131e+16</v>
+        <v>2.334035884572252e+16</v>
       </c>
       <c r="E2" t="inlineStr"/>
       <c r="F2" t="n">
-        <v>1220737884.511138</v>
-      </c>
-      <c r="G2" t="inlineStr"/>
-      <c r="H2" t="inlineStr"/>
+        <v>8690325973.251732</v>
+      </c>
+      <c r="G2" t="n">
+        <v>2695896622.694156</v>
+      </c>
+      <c r="H2" t="n">
+        <v>2695896622.694156</v>
+      </c>
       <c r="I2" t="n">
-        <v>0.4283520721267287</v>
+        <v>1.582457836931127</v>
       </c>
       <c r="J2" t="n">
-        <v>0.7223272640238989</v>
+        <v>3.223538284107874</v>
       </c>
       <c r="K2" t="n">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="L2" t="n">
-        <v>1.05</v>
+        <v>1.15</v>
       </c>
       <c r="M2" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="N2" t="n">
-        <v>100</v>
+        <v>2000</v>
       </c>
       <c r="O2" t="n">
-        <v>0.9</v>
+        <v>0.7</v>
       </c>
       <c r="P2" t="inlineStr">
         <is>
@@ -1955,14 +1967,14 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="R2" t="n">
-        <v>46889</v>
+        <v>183137</v>
       </c>
       <c r="S2" t="inlineStr"/>
       <c r="T2" t="n">
-        <v>2e+20</v>
+        <v>1.5e+20</v>
       </c>
       <c r="U2" t="n">
         <v>1.111111111111111e-07</v>
@@ -1971,20 +1983,20 @@
         <v>1</v>
       </c>
       <c r="W2" t="n">
-        <v>130810264.9008073</v>
+        <v>25122053.04922638</v>
       </c>
       <c r="X2" t="n">
         <v>21600</v>
       </c>
       <c r="Y2" t="n">
-        <v>7200</v>
+        <v>43200</v>
       </c>
       <c r="Z2" t="inlineStr"/>
       <c r="AA2" t="n">
-        <v>0.1</v>
+        <v>0.5</v>
       </c>
       <c r="AB2" t="n">
-        <v>2599566395.617924</v>
+        <v>2593373205.080279</v>
       </c>
     </row>
     <row r="3">
@@ -2250,18 +2262,22 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>ddstartup_20251111_220719_parametric_T_seeded</t>
+          <t>ddstartup_20251112_105650_parametric_T_seeded</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>29108529538990.68</v>
+        <v>29124796695359.91</v>
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="n">
         <v>39242642.39628718</v>
       </c>
-      <c r="H2" t="inlineStr"/>
-      <c r="I2" t="inlineStr"/>
+      <c r="H2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2" t="n">
+        <v>0</v>
+      </c>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="n">
@@ -2301,7 +2317,7 @@
         <v>1</v>
       </c>
       <c r="X2" t="n">
-        <v>7215539.020025951</v>
+        <v>7214472.388090405</v>
       </c>
       <c r="Y2" t="n">
         <v>14400</v>
@@ -2314,7 +2330,7 @@
         <v>5</v>
       </c>
       <c r="AC2" t="n">
-        <v>808570.2649719634</v>
+        <v>809022.1304266643</v>
       </c>
     </row>
     <row r="3">
@@ -2420,22 +2436,30 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>ddstartup_20251111_220719_parametric_T_seeded</t>
+          <t>ddstartup_20251112_105650_parametric_T_seeded</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1144814713425666</v>
+        <v>1138013507319482</v>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="n">
-        <v>3433325300.187575</v>
-      </c>
-      <c r="H4" t="inlineStr"/>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
+        <v>686665060.037515</v>
+      </c>
+      <c r="H4" t="n">
+        <v>13353444.38973963</v>
+      </c>
+      <c r="I4" t="n">
+        <v>13353444.38973963</v>
+      </c>
+      <c r="J4" t="n">
+        <v>22.02779995948626</v>
+      </c>
+      <c r="K4" t="n">
+        <v>51.42231771790108</v>
+      </c>
       <c r="L4" t="n">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="M4" t="n">
         <v>1.3</v>
@@ -2444,10 +2468,10 @@
         <v>20</v>
       </c>
       <c r="O4" t="n">
-        <v>500</v>
+        <v>100</v>
       </c>
       <c r="P4" t="n">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
@@ -2458,7 +2482,7 @@
         <v>0.4</v>
       </c>
       <c r="S4" t="n">
-        <v>98955</v>
+        <v>45192</v>
       </c>
       <c r="T4" t="inlineStr"/>
       <c r="U4" t="n">
@@ -2471,20 +2495,20 @@
         <v>1</v>
       </c>
       <c r="X4" t="n">
-        <v>2761668.130031304</v>
+        <v>10354514.57400635</v>
       </c>
       <c r="Y4" t="n">
         <v>43200</v>
       </c>
       <c r="Z4" t="n">
-        <v>43200</v>
+        <v>86400</v>
       </c>
       <c r="AA4" t="inlineStr"/>
       <c r="AB4" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="AC4" t="n">
-        <v>31800408.7062685</v>
+        <v>31611486.31443005</v>
       </c>
     </row>
     <row r="5">
@@ -2501,22 +2525,26 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>ddstartup_20251111_220719_parametric_T_seeded</t>
+          <t>ddstartup_20251112_105650_parametric_T_seeded</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2873704111383478</v>
+        <v>2860619151416868</v>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="n">
-        <v>1601740505.970906</v>
-      </c>
-      <c r="H5" t="inlineStr"/>
-      <c r="I5" t="inlineStr"/>
+        <v>784852847.9257437</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0</v>
+      </c>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="n">
-        <v>0.5</v>
+        <v>0.75</v>
       </c>
       <c r="M5" t="n">
         <v>1.05</v>
@@ -2525,10 +2553,10 @@
         <v>10</v>
       </c>
       <c r="O5" t="n">
-        <v>500</v>
+        <v>2000</v>
       </c>
       <c r="P5" t="n">
-        <v>0.9</v>
+        <v>0.7</v>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
@@ -2539,11 +2567,11 @@
         <v>0.4</v>
       </c>
       <c r="S5" t="n">
-        <v>68577</v>
+        <v>162084</v>
       </c>
       <c r="T5" t="inlineStr"/>
       <c r="U5" t="n">
-        <v>2e+20</v>
+        <v>7e+19</v>
       </c>
       <c r="V5" t="n">
         <v>2.777777777777778e-08</v>
@@ -2552,20 +2580,20 @@
         <v>1</v>
       </c>
       <c r="X5" t="n">
-        <v>10091460.67619537</v>
+        <v>29653842.57663549</v>
       </c>
       <c r="Y5" t="n">
-        <v>14400</v>
+        <v>21600</v>
       </c>
       <c r="Z5" t="n">
-        <v>86400</v>
+        <v>43200</v>
       </c>
       <c r="AA5" t="inlineStr"/>
       <c r="AB5" t="n">
         <v>5</v>
       </c>
       <c r="AC5" t="n">
-        <v>79825114.2050966</v>
+        <v>79461643.09491301</v>
       </c>
     </row>
     <row r="6">
@@ -2671,23 +2699,27 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>ddstartup_20251111_220719_parametric_T_seeded</t>
+          <t>ddstartup_20251112_105650_parametric_T_seeded</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1445382109715489</v>
+        <v>1438819862135144</v>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="n">
-        <v>180195806.9217269</v>
-      </c>
-      <c r="H7" t="inlineStr"/>
-      <c r="I7" t="inlineStr"/>
+        <v>320348101.1941811</v>
+      </c>
+      <c r="H7" t="n">
+        <v>135631774.1917052</v>
+      </c>
+      <c r="I7" t="n">
+        <v>135631774.1917052</v>
+      </c>
       <c r="J7" t="n">
-        <v>0.9246077989589435</v>
+        <v>1.342598232693379</v>
       </c>
       <c r="K7" t="n">
-        <v>1.603994324979293</v>
+        <v>2.361895677493633</v>
       </c>
       <c r="L7" t="n">
         <v>0.75</v>
@@ -2702,7 +2734,7 @@
         <v>100</v>
       </c>
       <c r="P7" t="n">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
@@ -2713,11 +2745,11 @@
         <v>0.3</v>
       </c>
       <c r="S7" t="n">
-        <v>7457</v>
+        <v>13322</v>
       </c>
       <c r="T7" t="inlineStr"/>
       <c r="U7" t="n">
-        <v>1.5e+20</v>
+        <v>2e+20</v>
       </c>
       <c r="V7" t="n">
         <v>1.111111111111111e-07</v>
@@ -2726,20 +2758,20 @@
         <v>1</v>
       </c>
       <c r="X7" t="n">
-        <v>90178830.17408101</v>
+        <v>69382954.14868729</v>
       </c>
       <c r="Y7" t="n">
         <v>14400</v>
       </c>
       <c r="Z7" t="n">
-        <v>7200</v>
+        <v>86400</v>
       </c>
       <c r="AA7" t="inlineStr"/>
       <c r="AB7" t="n">
         <v>0.5</v>
       </c>
       <c r="AC7" t="n">
-        <v>160598012.1906099</v>
+        <v>159868873.5705715</v>
       </c>
     </row>
     <row r="8">
@@ -2845,31 +2877,39 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>ddstartup_20251111_220719_parametric_T_seeded</t>
+          <t>ddstartup_20251112_105650_parametric_T_seeded</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>4306303728546464</v>
+        <v>1.072577529918125e+16</v>
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="n">
-        <v>4345162986.625866</v>
-      </c>
-      <c r="H9" t="inlineStr"/>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
+        <v>686665060.037515</v>
+      </c>
+      <c r="H9" t="n">
+        <v>1311119244.38974</v>
+      </c>
+      <c r="I9" t="n">
+        <v>1311119244.38974</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0.2533857775249347</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0.5237243393198178</v>
+      </c>
       <c r="L9" t="n">
-        <v>0.75</v>
+        <v>0.5</v>
       </c>
       <c r="M9" t="n">
-        <v>1.05</v>
+        <v>1.15</v>
       </c>
       <c r="N9" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="O9" t="n">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="P9" t="n">
         <v>0.9</v>
@@ -2883,33 +2923,33 @@
         <v>0.4</v>
       </c>
       <c r="S9" t="n">
-        <v>132910</v>
+        <v>41397</v>
       </c>
       <c r="T9" t="inlineStr"/>
       <c r="U9" t="n">
         <v>1.5e+20</v>
       </c>
       <c r="V9" t="n">
-        <v>6.944444444444444e-08</v>
+        <v>2.777777777777778e-08</v>
       </c>
       <c r="W9" t="b">
         <v>1</v>
       </c>
       <c r="X9" t="n">
-        <v>6104968.50953293</v>
+        <v>84057409.69629706</v>
       </c>
       <c r="Y9" t="n">
         <v>21600</v>
       </c>
       <c r="Z9" t="n">
-        <v>7200</v>
+        <v>43200</v>
       </c>
       <c r="AA9" t="inlineStr"/>
       <c r="AB9" t="n">
-        <v>5</v>
+        <v>0.1</v>
       </c>
       <c r="AC9" t="n">
-        <v>299048870.0379488</v>
+        <v>297938202.7550347</v>
       </c>
     </row>
     <row r="10">
@@ -3017,35 +3057,39 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>ddstartup_20251111_220719_parametric_T_seeded</t>
+          <t>ddstartup_20251112_105650_parametric_T_seeded</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>7973024030576672</v>
+        <v>4960927498617498</v>
       </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="n">
-        <v>320348101.1941811</v>
-      </c>
-      <c r="H11" t="inlineStr"/>
-      <c r="I11" t="inlineStr"/>
+        <v>2990807817.052288</v>
+      </c>
+      <c r="H11" t="n">
+        <v>775938308.8975326</v>
+      </c>
+      <c r="I11" t="n">
+        <v>775938308.8975326</v>
+      </c>
       <c r="J11" t="n">
-        <v>0.1602146580159418</v>
+        <v>1.718276282484998</v>
       </c>
       <c r="K11" t="n">
-        <v>0.3541017240527546</v>
+        <v>3.854440208399663</v>
       </c>
       <c r="L11" t="n">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="M11" t="n">
         <v>1.3</v>
       </c>
       <c r="N11" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="O11" t="n">
-        <v>100</v>
+        <v>2000</v>
       </c>
       <c r="P11" t="n">
         <v>0.5</v>
@@ -3059,33 +3103,33 @@
         <v>0.3</v>
       </c>
       <c r="S11" t="n">
-        <v>12943</v>
+        <v>196796</v>
       </c>
       <c r="T11" t="inlineStr"/>
       <c r="U11" t="n">
-        <v>2e+20</v>
+        <v>7e+19</v>
       </c>
       <c r="V11" t="n">
-        <v>6.944444444444444e-08</v>
+        <v>1.111111111111111e-07</v>
       </c>
       <c r="W11" t="b">
         <v>1</v>
       </c>
       <c r="X11" t="n">
-        <v>303032258.2776924</v>
+        <v>19953075.7051578</v>
       </c>
       <c r="Y11" t="n">
         <v>43200</v>
       </c>
       <c r="Z11" t="n">
-        <v>86400</v>
+        <v>43200</v>
       </c>
       <c r="AA11" t="inlineStr"/>
       <c r="AB11" t="n">
-        <v>0.1</v>
+        <v>1</v>
       </c>
       <c r="AC11" t="n">
-        <v>553682224.3456022</v>
+        <v>551214166.5130553</v>
       </c>
     </row>
     <row r="12">
@@ -3191,23 +3235,27 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>ddstartup_20251111_220719_parametric_T_seeded</t>
+          <t>ddstartup_20251112_105650_parametric_T_seeded</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>3.900693602812538e+16</v>
+        <v>1.55444751200187e+16</v>
       </c>
       <c r="F13" t="inlineStr"/>
       <c r="G13" t="n">
-        <v>2172581493.312933</v>
-      </c>
-      <c r="H13" t="inlineStr"/>
-      <c r="I13" t="inlineStr"/>
+        <v>3862367099.222991</v>
+      </c>
+      <c r="H13" t="n">
+        <v>717522276.7529577</v>
+      </c>
+      <c r="I13" t="n">
+        <v>717522276.7529577</v>
+      </c>
       <c r="J13" t="n">
-        <v>0.2512639821194254</v>
+        <v>2.950840798869634</v>
       </c>
       <c r="K13" t="n">
-        <v>0.4345284519303243</v>
+        <v>5.38292290617313</v>
       </c>
       <c r="L13" t="n">
         <v>0.5</v>
@@ -3222,7 +3270,7 @@
         <v>500</v>
       </c>
       <c r="P13" t="n">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
@@ -3233,20 +3281,20 @@
         <v>0.4</v>
       </c>
       <c r="S13" t="n">
-        <v>75861</v>
+        <v>83155</v>
       </c>
       <c r="T13" t="inlineStr"/>
       <c r="U13" t="n">
-        <v>1.5e+20</v>
+        <v>2e+20</v>
       </c>
       <c r="V13" t="n">
-        <v>2.777777777777778e-08</v>
+        <v>6.944444444444444e-08</v>
       </c>
       <c r="W13" t="b">
         <v>1</v>
       </c>
       <c r="X13" t="n">
-        <v>212851007.5009588</v>
+        <v>31812984.14464649</v>
       </c>
       <c r="Y13" t="n">
         <v>14400</v>
@@ -3256,10 +3304,10 @@
       </c>
       <c r="AA13" t="inlineStr"/>
       <c r="AB13" t="n">
-        <v>0.1</v>
+        <v>0.5</v>
       </c>
       <c r="AC13" t="n">
-        <v>1083526000.78126</v>
+        <v>1079477438.890187</v>
       </c>
     </row>
     <row r="14">
@@ -3367,38 +3415,42 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>ddstartup_20251111_220719_parametric_T_seeded</t>
+          <t>ddstartup_20251112_105650_parametric_T_seeded</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>2.339609756056131e+16</v>
+        <v>2.334035884572252e+16</v>
       </c>
       <c r="F15" t="inlineStr"/>
       <c r="G15" t="n">
-        <v>1220737884.511138</v>
-      </c>
-      <c r="H15" t="inlineStr"/>
-      <c r="I15" t="inlineStr"/>
+        <v>8690325973.251732</v>
+      </c>
+      <c r="H15" t="n">
+        <v>2695896622.694156</v>
+      </c>
+      <c r="I15" t="n">
+        <v>2695896622.694156</v>
+      </c>
       <c r="J15" t="n">
-        <v>0.4283520721267287</v>
+        <v>1.582457836931127</v>
       </c>
       <c r="K15" t="n">
-        <v>0.7223272640238989</v>
+        <v>3.223538284107874</v>
       </c>
       <c r="L15" t="n">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="M15" t="n">
-        <v>1.05</v>
+        <v>1.15</v>
       </c>
       <c r="N15" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="O15" t="n">
-        <v>100</v>
+        <v>2000</v>
       </c>
       <c r="P15" t="n">
-        <v>0.9</v>
+        <v>0.7</v>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
@@ -3406,14 +3458,14 @@
         </is>
       </c>
       <c r="R15" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="S15" t="n">
-        <v>46889</v>
+        <v>183137</v>
       </c>
       <c r="T15" t="inlineStr"/>
       <c r="U15" t="n">
-        <v>2e+20</v>
+        <v>1.5e+20</v>
       </c>
       <c r="V15" t="n">
         <v>1.111111111111111e-07</v>
@@ -3422,20 +3474,20 @@
         <v>1</v>
       </c>
       <c r="X15" t="n">
-        <v>130810264.9008073</v>
+        <v>25122053.04922638</v>
       </c>
       <c r="Y15" t="n">
         <v>21600</v>
       </c>
       <c r="Z15" t="n">
-        <v>7200</v>
+        <v>43200</v>
       </c>
       <c r="AA15" t="inlineStr"/>
       <c r="AB15" t="n">
-        <v>0.1</v>
+        <v>0.5</v>
       </c>
       <c r="AC15" t="n">
-        <v>2599566395.617924</v>
+        <v>2593373205.080279</v>
       </c>
     </row>
     <row r="16">
@@ -3785,18 +3837,22 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>ddstartup_20251111_220719_parametric_T_seeded</t>
+          <t>ddstartup_20251112_105650_parametric_T_seeded</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>29108529538990.68</v>
+        <v>29124796695359.91</v>
       </c>
       <c r="E2" t="inlineStr"/>
       <c r="F2" t="n">
         <v>39242642.39628718</v>
       </c>
-      <c r="G2" t="inlineStr"/>
-      <c r="H2" t="inlineStr"/>
+      <c r="G2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2" t="n">
+        <v>0</v>
+      </c>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="n">
@@ -3836,7 +3892,7 @@
         <v>1</v>
       </c>
       <c r="W2" t="n">
-        <v>7215539.020025951</v>
+        <v>7214472.388090405</v>
       </c>
       <c r="X2" t="n">
         <v>14400</v>
@@ -3849,7 +3905,7 @@
         <v>5</v>
       </c>
       <c r="AB2" t="n">
-        <v>808570.2649719634</v>
+        <v>809022.1304266643</v>
       </c>
     </row>
     <row r="3">
@@ -3863,22 +3919,30 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>ddstartup_20251111_220719_parametric_T_seeded</t>
+          <t>ddstartup_20251112_105650_parametric_T_seeded</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>1144814713425666</v>
+        <v>1138013507319482</v>
       </c>
       <c r="E3" t="inlineStr"/>
       <c r="F3" t="n">
-        <v>3433325300.187575</v>
-      </c>
-      <c r="G3" t="inlineStr"/>
-      <c r="H3" t="inlineStr"/>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
+        <v>686665060.037515</v>
+      </c>
+      <c r="G3" t="n">
+        <v>13353444.38973963</v>
+      </c>
+      <c r="H3" t="n">
+        <v>13353444.38973963</v>
+      </c>
+      <c r="I3" t="n">
+        <v>22.02779995948626</v>
+      </c>
+      <c r="J3" t="n">
+        <v>51.42231771790108</v>
+      </c>
       <c r="K3" t="n">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="L3" t="n">
         <v>1.3</v>
@@ -3887,10 +3951,10 @@
         <v>20</v>
       </c>
       <c r="N3" t="n">
-        <v>500</v>
+        <v>100</v>
       </c>
       <c r="O3" t="n">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
       <c r="P3" t="inlineStr">
         <is>
@@ -3901,7 +3965,7 @@
         <v>0.4</v>
       </c>
       <c r="R3" t="n">
-        <v>98955</v>
+        <v>45192</v>
       </c>
       <c r="S3" t="inlineStr"/>
       <c r="T3" t="n">
@@ -3914,20 +3978,20 @@
         <v>1</v>
       </c>
       <c r="W3" t="n">
-        <v>2761668.130031304</v>
+        <v>10354514.57400635</v>
       </c>
       <c r="X3" t="n">
         <v>43200</v>
       </c>
       <c r="Y3" t="n">
-        <v>43200</v>
+        <v>86400</v>
       </c>
       <c r="Z3" t="inlineStr"/>
       <c r="AA3" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="AB3" t="n">
-        <v>31800408.7062685</v>
+        <v>31611486.31443005</v>
       </c>
     </row>
     <row r="4">
@@ -3941,22 +4005,26 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>ddstartup_20251111_220719_parametric_T_seeded</t>
+          <t>ddstartup_20251112_105650_parametric_T_seeded</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>2873704111383478</v>
+        <v>2860619151416868</v>
       </c>
       <c r="E4" t="inlineStr"/>
       <c r="F4" t="n">
-        <v>1601740505.970906</v>
-      </c>
-      <c r="G4" t="inlineStr"/>
-      <c r="H4" t="inlineStr"/>
+        <v>784852847.9257437</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0</v>
+      </c>
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="n">
-        <v>0.5</v>
+        <v>0.75</v>
       </c>
       <c r="L4" t="n">
         <v>1.05</v>
@@ -3965,10 +4033,10 @@
         <v>10</v>
       </c>
       <c r="N4" t="n">
-        <v>500</v>
+        <v>2000</v>
       </c>
       <c r="O4" t="n">
-        <v>0.9</v>
+        <v>0.7</v>
       </c>
       <c r="P4" t="inlineStr">
         <is>
@@ -3979,11 +4047,11 @@
         <v>0.4</v>
       </c>
       <c r="R4" t="n">
-        <v>68577</v>
+        <v>162084</v>
       </c>
       <c r="S4" t="inlineStr"/>
       <c r="T4" t="n">
-        <v>2e+20</v>
+        <v>7e+19</v>
       </c>
       <c r="U4" t="n">
         <v>2.777777777777778e-08</v>
@@ -3992,20 +4060,20 @@
         <v>1</v>
       </c>
       <c r="W4" t="n">
-        <v>10091460.67619537</v>
+        <v>29653842.57663549</v>
       </c>
       <c r="X4" t="n">
-        <v>14400</v>
+        <v>21600</v>
       </c>
       <c r="Y4" t="n">
-        <v>86400</v>
+        <v>43200</v>
       </c>
       <c r="Z4" t="inlineStr"/>
       <c r="AA4" t="n">
         <v>5</v>
       </c>
       <c r="AB4" t="n">
-        <v>79825114.2050966</v>
+        <v>79461643.09491301</v>
       </c>
     </row>
     <row r="5">
@@ -4019,23 +4087,27 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>ddstartup_20251111_220719_parametric_T_seeded</t>
+          <t>ddstartup_20251112_105650_parametric_T_seeded</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>1445382109715489</v>
+        <v>1438819862135144</v>
       </c>
       <c r="E5" t="inlineStr"/>
       <c r="F5" t="n">
-        <v>180195806.9217269</v>
-      </c>
-      <c r="G5" t="inlineStr"/>
-      <c r="H5" t="inlineStr"/>
+        <v>320348101.1941811</v>
+      </c>
+      <c r="G5" t="n">
+        <v>135631774.1917052</v>
+      </c>
+      <c r="H5" t="n">
+        <v>135631774.1917052</v>
+      </c>
       <c r="I5" t="n">
-        <v>0.9246077989589435</v>
+        <v>1.342598232693379</v>
       </c>
       <c r="J5" t="n">
-        <v>1.603994324979293</v>
+        <v>2.361895677493633</v>
       </c>
       <c r="K5" t="n">
         <v>0.75</v>
@@ -4050,7 +4122,7 @@
         <v>100</v>
       </c>
       <c r="O5" t="n">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="P5" t="inlineStr">
         <is>
@@ -4061,11 +4133,11 @@
         <v>0.3</v>
       </c>
       <c r="R5" t="n">
-        <v>7457</v>
+        <v>13322</v>
       </c>
       <c r="S5" t="inlineStr"/>
       <c r="T5" t="n">
-        <v>1.5e+20</v>
+        <v>2e+20</v>
       </c>
       <c r="U5" t="n">
         <v>1.111111111111111e-07</v>
@@ -4074,20 +4146,20 @@
         <v>1</v>
       </c>
       <c r="W5" t="n">
-        <v>90178830.17408101</v>
+        <v>69382954.14868729</v>
       </c>
       <c r="X5" t="n">
         <v>14400</v>
       </c>
       <c r="Y5" t="n">
-        <v>7200</v>
+        <v>86400</v>
       </c>
       <c r="Z5" t="inlineStr"/>
       <c r="AA5" t="n">
         <v>0.5</v>
       </c>
       <c r="AB5" t="n">
-        <v>160598012.1906099</v>
+        <v>159868873.5705715</v>
       </c>
     </row>
     <row r="6">
@@ -4101,31 +4173,39 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>ddstartup_20251111_220719_parametric_T_seeded</t>
+          <t>ddstartup_20251112_105650_parametric_T_seeded</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>4306303728546464</v>
+        <v>1.072577529918125e+16</v>
       </c>
       <c r="E6" t="inlineStr"/>
       <c r="F6" t="n">
-        <v>4345162986.625866</v>
-      </c>
-      <c r="G6" t="inlineStr"/>
-      <c r="H6" t="inlineStr"/>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
+        <v>686665060.037515</v>
+      </c>
+      <c r="G6" t="n">
+        <v>1311119244.38974</v>
+      </c>
+      <c r="H6" t="n">
+        <v>1311119244.38974</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0.2533857775249347</v>
+      </c>
+      <c r="J6" t="n">
+        <v>0.5237243393198178</v>
+      </c>
       <c r="K6" t="n">
-        <v>0.75</v>
+        <v>0.5</v>
       </c>
       <c r="L6" t="n">
-        <v>1.05</v>
+        <v>1.15</v>
       </c>
       <c r="M6" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="N6" t="n">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="O6" t="n">
         <v>0.9</v>
@@ -4139,33 +4219,33 @@
         <v>0.4</v>
       </c>
       <c r="R6" t="n">
-        <v>132910</v>
+        <v>41397</v>
       </c>
       <c r="S6" t="inlineStr"/>
       <c r="T6" t="n">
         <v>1.5e+20</v>
       </c>
       <c r="U6" t="n">
-        <v>6.944444444444444e-08</v>
+        <v>2.777777777777778e-08</v>
       </c>
       <c r="V6" t="b">
         <v>1</v>
       </c>
       <c r="W6" t="n">
-        <v>6104968.50953293</v>
+        <v>84057409.69629706</v>
       </c>
       <c r="X6" t="n">
         <v>21600</v>
       </c>
       <c r="Y6" t="n">
-        <v>7200</v>
+        <v>43200</v>
       </c>
       <c r="Z6" t="inlineStr"/>
       <c r="AA6" t="n">
-        <v>5</v>
+        <v>0.1</v>
       </c>
       <c r="AB6" t="n">
-        <v>299048870.0379488</v>
+        <v>297938202.7550347</v>
       </c>
     </row>
     <row r="7">
@@ -4179,35 +4259,39 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>ddstartup_20251111_220719_parametric_T_seeded</t>
+          <t>ddstartup_20251112_105650_parametric_T_seeded</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>7973024030576672</v>
+        <v>4960927498617498</v>
       </c>
       <c r="E7" t="inlineStr"/>
       <c r="F7" t="n">
-        <v>320348101.1941811</v>
-      </c>
-      <c r="G7" t="inlineStr"/>
-      <c r="H7" t="inlineStr"/>
+        <v>2990807817.052288</v>
+      </c>
+      <c r="G7" t="n">
+        <v>775938308.8975326</v>
+      </c>
+      <c r="H7" t="n">
+        <v>775938308.8975326</v>
+      </c>
       <c r="I7" t="n">
-        <v>0.1602146580159418</v>
+        <v>1.718276282484998</v>
       </c>
       <c r="J7" t="n">
-        <v>0.3541017240527546</v>
+        <v>3.854440208399663</v>
       </c>
       <c r="K7" t="n">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="L7" t="n">
         <v>1.3</v>
       </c>
       <c r="M7" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="N7" t="n">
-        <v>100</v>
+        <v>2000</v>
       </c>
       <c r="O7" t="n">
         <v>0.5</v>
@@ -4221,33 +4305,33 @@
         <v>0.3</v>
       </c>
       <c r="R7" t="n">
-        <v>12943</v>
+        <v>196796</v>
       </c>
       <c r="S7" t="inlineStr"/>
       <c r="T7" t="n">
-        <v>2e+20</v>
+        <v>7e+19</v>
       </c>
       <c r="U7" t="n">
-        <v>6.944444444444444e-08</v>
+        <v>1.111111111111111e-07</v>
       </c>
       <c r="V7" t="b">
         <v>1</v>
       </c>
       <c r="W7" t="n">
-        <v>303032258.2776924</v>
+        <v>19953075.7051578</v>
       </c>
       <c r="X7" t="n">
         <v>43200</v>
       </c>
       <c r="Y7" t="n">
-        <v>86400</v>
+        <v>43200</v>
       </c>
       <c r="Z7" t="inlineStr"/>
       <c r="AA7" t="n">
-        <v>0.1</v>
+        <v>1</v>
       </c>
       <c r="AB7" t="n">
-        <v>553682224.3456022</v>
+        <v>551214166.5130553</v>
       </c>
     </row>
     <row r="8">
@@ -4261,23 +4345,27 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>ddstartup_20251111_220719_parametric_T_seeded</t>
+          <t>ddstartup_20251112_105650_parametric_T_seeded</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>3.900693602812538e+16</v>
+        <v>1.55444751200187e+16</v>
       </c>
       <c r="E8" t="inlineStr"/>
       <c r="F8" t="n">
-        <v>2172581493.312933</v>
-      </c>
-      <c r="G8" t="inlineStr"/>
-      <c r="H8" t="inlineStr"/>
+        <v>3862367099.222991</v>
+      </c>
+      <c r="G8" t="n">
+        <v>717522276.7529577</v>
+      </c>
+      <c r="H8" t="n">
+        <v>717522276.7529577</v>
+      </c>
       <c r="I8" t="n">
-        <v>0.2512639821194254</v>
+        <v>2.950840798869634</v>
       </c>
       <c r="J8" t="n">
-        <v>0.4345284519303243</v>
+        <v>5.38292290617313</v>
       </c>
       <c r="K8" t="n">
         <v>0.5</v>
@@ -4292,7 +4380,7 @@
         <v>500</v>
       </c>
       <c r="O8" t="n">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
       <c r="P8" t="inlineStr">
         <is>
@@ -4303,20 +4391,20 @@
         <v>0.4</v>
       </c>
       <c r="R8" t="n">
-        <v>75861</v>
+        <v>83155</v>
       </c>
       <c r="S8" t="inlineStr"/>
       <c r="T8" t="n">
-        <v>1.5e+20</v>
+        <v>2e+20</v>
       </c>
       <c r="U8" t="n">
-        <v>2.777777777777778e-08</v>
+        <v>6.944444444444444e-08</v>
       </c>
       <c r="V8" t="b">
         <v>1</v>
       </c>
       <c r="W8" t="n">
-        <v>212851007.5009588</v>
+        <v>31812984.14464649</v>
       </c>
       <c r="X8" t="n">
         <v>14400</v>
@@ -4326,10 +4414,10 @@
       </c>
       <c r="Z8" t="inlineStr"/>
       <c r="AA8" t="n">
-        <v>0.1</v>
+        <v>0.5</v>
       </c>
       <c r="AB8" t="n">
-        <v>1083526000.78126</v>
+        <v>1079477438.890187</v>
       </c>
     </row>
     <row r="9">
@@ -4343,38 +4431,42 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>ddstartup_20251111_220719_parametric_T_seeded</t>
+          <t>ddstartup_20251112_105650_parametric_T_seeded</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>2.339609756056131e+16</v>
+        <v>2.334035884572252e+16</v>
       </c>
       <c r="E9" t="inlineStr"/>
       <c r="F9" t="n">
-        <v>1220737884.511138</v>
-      </c>
-      <c r="G9" t="inlineStr"/>
-      <c r="H9" t="inlineStr"/>
+        <v>8690325973.251732</v>
+      </c>
+      <c r="G9" t="n">
+        <v>2695896622.694156</v>
+      </c>
+      <c r="H9" t="n">
+        <v>2695896622.694156</v>
+      </c>
       <c r="I9" t="n">
-        <v>0.4283520721267287</v>
+        <v>1.582457836931127</v>
       </c>
       <c r="J9" t="n">
-        <v>0.7223272640238989</v>
+        <v>3.223538284107874</v>
       </c>
       <c r="K9" t="n">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="L9" t="n">
-        <v>1.05</v>
+        <v>1.15</v>
       </c>
       <c r="M9" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="N9" t="n">
-        <v>100</v>
+        <v>2000</v>
       </c>
       <c r="O9" t="n">
-        <v>0.9</v>
+        <v>0.7</v>
       </c>
       <c r="P9" t="inlineStr">
         <is>
@@ -4382,14 +4474,14 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="R9" t="n">
-        <v>46889</v>
+        <v>183137</v>
       </c>
       <c r="S9" t="inlineStr"/>
       <c r="T9" t="n">
-        <v>2e+20</v>
+        <v>1.5e+20</v>
       </c>
       <c r="U9" t="n">
         <v>1.111111111111111e-07</v>
@@ -4398,20 +4490,20 @@
         <v>1</v>
       </c>
       <c r="W9" t="n">
-        <v>130810264.9008073</v>
+        <v>25122053.04922638</v>
       </c>
       <c r="X9" t="n">
         <v>21600</v>
       </c>
       <c r="Y9" t="n">
-        <v>7200</v>
+        <v>43200</v>
       </c>
       <c r="Z9" t="inlineStr"/>
       <c r="AA9" t="n">
-        <v>0.1</v>
+        <v>0.5</v>
       </c>
       <c r="AB9" t="n">
-        <v>2599566395.617924</v>
+        <v>2593373205.080279</v>
       </c>
     </row>
   </sheetData>
@@ -5431,18 +5523,22 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>ddstartup_20251111_220719_parametric_T_seeded</t>
+          <t>ddstartup_20251112_105650_parametric_T_seeded</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>29108529538990.68</v>
+        <v>29124796695359.91</v>
       </c>
       <c r="E2" t="inlineStr"/>
       <c r="F2" t="n">
         <v>39242642.39628718</v>
       </c>
-      <c r="G2" t="inlineStr"/>
-      <c r="H2" t="inlineStr"/>
+      <c r="G2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2" t="n">
+        <v>0</v>
+      </c>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="n">
@@ -5482,7 +5578,7 @@
         <v>1</v>
       </c>
       <c r="W2" t="n">
-        <v>7215539.020025951</v>
+        <v>7214472.388090405</v>
       </c>
       <c r="X2" t="n">
         <v>14400</v>
@@ -5495,7 +5591,7 @@
         <v>5</v>
       </c>
       <c r="AB2" t="n">
-        <v>808570.2649719634</v>
+        <v>809022.1304266643</v>
       </c>
     </row>
     <row r="3">
@@ -5751,22 +5847,30 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>ddstartup_20251111_220719_parametric_T_seeded</t>
+          <t>ddstartup_20251112_105650_parametric_T_seeded</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>1144814713425666</v>
+        <v>1138013507319482</v>
       </c>
       <c r="E2" t="inlineStr"/>
       <c r="F2" t="n">
-        <v>3433325300.187575</v>
-      </c>
-      <c r="G2" t="inlineStr"/>
-      <c r="H2" t="inlineStr"/>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
+        <v>686665060.037515</v>
+      </c>
+      <c r="G2" t="n">
+        <v>13353444.38973963</v>
+      </c>
+      <c r="H2" t="n">
+        <v>13353444.38973963</v>
+      </c>
+      <c r="I2" t="n">
+        <v>22.02779995948626</v>
+      </c>
+      <c r="J2" t="n">
+        <v>51.42231771790108</v>
+      </c>
       <c r="K2" t="n">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="L2" t="n">
         <v>1.3</v>
@@ -5775,10 +5879,10 @@
         <v>20</v>
       </c>
       <c r="N2" t="n">
-        <v>500</v>
+        <v>100</v>
       </c>
       <c r="O2" t="n">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
       <c r="P2" t="inlineStr">
         <is>
@@ -5789,7 +5893,7 @@
         <v>0.4</v>
       </c>
       <c r="R2" t="n">
-        <v>98955</v>
+        <v>45192</v>
       </c>
       <c r="S2" t="inlineStr"/>
       <c r="T2" t="n">
@@ -5802,20 +5906,20 @@
         <v>1</v>
       </c>
       <c r="W2" t="n">
-        <v>2761668.130031304</v>
+        <v>10354514.57400635</v>
       </c>
       <c r="X2" t="n">
         <v>43200</v>
       </c>
       <c r="Y2" t="n">
-        <v>43200</v>
+        <v>86400</v>
       </c>
       <c r="Z2" t="inlineStr"/>
       <c r="AA2" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="AB2" t="n">
-        <v>31800408.7062685</v>
+        <v>31611486.31443005</v>
       </c>
     </row>
     <row r="3">
@@ -6071,22 +6175,26 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>ddstartup_20251111_220719_parametric_T_seeded</t>
+          <t>ddstartup_20251112_105650_parametric_T_seeded</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>2873704111383478</v>
+        <v>2860619151416868</v>
       </c>
       <c r="E2" t="inlineStr"/>
       <c r="F2" t="n">
-        <v>1601740505.970906</v>
-      </c>
-      <c r="G2" t="inlineStr"/>
-      <c r="H2" t="inlineStr"/>
+        <v>784852847.9257437</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2" t="n">
+        <v>0</v>
+      </c>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="n">
-        <v>0.5</v>
+        <v>0.75</v>
       </c>
       <c r="L2" t="n">
         <v>1.05</v>
@@ -6095,10 +6203,10 @@
         <v>10</v>
       </c>
       <c r="N2" t="n">
-        <v>500</v>
+        <v>2000</v>
       </c>
       <c r="O2" t="n">
-        <v>0.9</v>
+        <v>0.7</v>
       </c>
       <c r="P2" t="inlineStr">
         <is>
@@ -6109,11 +6217,11 @@
         <v>0.4</v>
       </c>
       <c r="R2" t="n">
-        <v>68577</v>
+        <v>162084</v>
       </c>
       <c r="S2" t="inlineStr"/>
       <c r="T2" t="n">
-        <v>2e+20</v>
+        <v>7e+19</v>
       </c>
       <c r="U2" t="n">
         <v>2.777777777777778e-08</v>
@@ -6122,20 +6230,20 @@
         <v>1</v>
       </c>
       <c r="W2" t="n">
-        <v>10091460.67619537</v>
+        <v>29653842.57663549</v>
       </c>
       <c r="X2" t="n">
-        <v>14400</v>
+        <v>21600</v>
       </c>
       <c r="Y2" t="n">
-        <v>86400</v>
+        <v>43200</v>
       </c>
       <c r="Z2" t="inlineStr"/>
       <c r="AA2" t="n">
         <v>5</v>
       </c>
       <c r="AB2" t="n">
-        <v>79825114.2050966</v>
+        <v>79461643.09491301</v>
       </c>
     </row>
     <row r="3">
@@ -6391,23 +6499,27 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>ddstartup_20251111_220719_parametric_T_seeded</t>
+          <t>ddstartup_20251112_105650_parametric_T_seeded</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>1445382109715489</v>
+        <v>1438819862135144</v>
       </c>
       <c r="E2" t="inlineStr"/>
       <c r="F2" t="n">
-        <v>180195806.9217269</v>
-      </c>
-      <c r="G2" t="inlineStr"/>
-      <c r="H2" t="inlineStr"/>
+        <v>320348101.1941811</v>
+      </c>
+      <c r="G2" t="n">
+        <v>135631774.1917052</v>
+      </c>
+      <c r="H2" t="n">
+        <v>135631774.1917052</v>
+      </c>
       <c r="I2" t="n">
-        <v>0.9246077989589435</v>
+        <v>1.342598232693379</v>
       </c>
       <c r="J2" t="n">
-        <v>1.603994324979293</v>
+        <v>2.361895677493633</v>
       </c>
       <c r="K2" t="n">
         <v>0.75</v>
@@ -6422,7 +6534,7 @@
         <v>100</v>
       </c>
       <c r="O2" t="n">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="P2" t="inlineStr">
         <is>
@@ -6433,11 +6545,11 @@
         <v>0.3</v>
       </c>
       <c r="R2" t="n">
-        <v>7457</v>
+        <v>13322</v>
       </c>
       <c r="S2" t="inlineStr"/>
       <c r="T2" t="n">
-        <v>1.5e+20</v>
+        <v>2e+20</v>
       </c>
       <c r="U2" t="n">
         <v>1.111111111111111e-07</v>
@@ -6446,20 +6558,20 @@
         <v>1</v>
       </c>
       <c r="W2" t="n">
-        <v>90178830.17408101</v>
+        <v>69382954.14868729</v>
       </c>
       <c r="X2" t="n">
         <v>14400</v>
       </c>
       <c r="Y2" t="n">
-        <v>7200</v>
+        <v>86400</v>
       </c>
       <c r="Z2" t="inlineStr"/>
       <c r="AA2" t="n">
         <v>0.5</v>
       </c>
       <c r="AB2" t="n">
-        <v>160598012.1906099</v>
+        <v>159868873.5705715</v>
       </c>
     </row>
     <row r="3">
@@ -6717,31 +6829,39 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>ddstartup_20251111_220719_parametric_T_seeded</t>
+          <t>ddstartup_20251112_105650_parametric_T_seeded</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>4306303728546464</v>
+        <v>1.072577529918125e+16</v>
       </c>
       <c r="E2" t="inlineStr"/>
       <c r="F2" t="n">
-        <v>4345162986.625866</v>
-      </c>
-      <c r="G2" t="inlineStr"/>
-      <c r="H2" t="inlineStr"/>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
+        <v>686665060.037515</v>
+      </c>
+      <c r="G2" t="n">
+        <v>1311119244.38974</v>
+      </c>
+      <c r="H2" t="n">
+        <v>1311119244.38974</v>
+      </c>
+      <c r="I2" t="n">
+        <v>0.2533857775249347</v>
+      </c>
+      <c r="J2" t="n">
+        <v>0.5237243393198178</v>
+      </c>
       <c r="K2" t="n">
-        <v>0.75</v>
+        <v>0.5</v>
       </c>
       <c r="L2" t="n">
-        <v>1.05</v>
+        <v>1.15</v>
       </c>
       <c r="M2" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="N2" t="n">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="O2" t="n">
         <v>0.9</v>
@@ -6755,33 +6875,33 @@
         <v>0.4</v>
       </c>
       <c r="R2" t="n">
-        <v>132910</v>
+        <v>41397</v>
       </c>
       <c r="S2" t="inlineStr"/>
       <c r="T2" t="n">
         <v>1.5e+20</v>
       </c>
       <c r="U2" t="n">
-        <v>6.944444444444444e-08</v>
+        <v>2.777777777777778e-08</v>
       </c>
       <c r="V2" t="b">
         <v>1</v>
       </c>
       <c r="W2" t="n">
-        <v>6104968.50953293</v>
+        <v>84057409.69629706</v>
       </c>
       <c r="X2" t="n">
         <v>21600</v>
       </c>
       <c r="Y2" t="n">
-        <v>7200</v>
+        <v>43200</v>
       </c>
       <c r="Z2" t="inlineStr"/>
       <c r="AA2" t="n">
-        <v>5</v>
+        <v>0.1</v>
       </c>
       <c r="AB2" t="n">
-        <v>299048870.0379488</v>
+        <v>297938202.7550347</v>
       </c>
     </row>
     <row r="3">

--- a/outputs/compare_tseeded_lump_unrealized_profits.xlsx
+++ b/outputs/compare_tseeded_lump_unrealized_profits.xlsx
@@ -2645,13 +2645,13 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>2.884764946099001e+16</v>
+        <v>5.769529892198002e+16</v>
       </c>
       <c r="E3" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="F3" t="n">
-        <v>12207378845.11138</v>
+        <v>24414757690.22276</v>
       </c>
       <c r="G3" t="n">
         <v>0.2067897919490654</v>
@@ -2667,7 +2667,7 @@
         <v>20</v>
       </c>
       <c r="L3" t="n">
-        <v>1000</v>
+        <v>2000</v>
       </c>
       <c r="M3" t="n">
         <v>0.7</v>
@@ -2681,7 +2681,7 @@
         <v>0.3</v>
       </c>
       <c r="P3" t="n">
-        <v>2981040</v>
+        <v>4976946</v>
       </c>
       <c r="Q3" t="n">
         <v>4.79379534335385e+16</v>
@@ -2690,7 +2690,7 @@
         <v>2e+20</v>
       </c>
       <c r="S3" t="n">
-        <v>1.111111111111111e-07</v>
+        <v>5.555555555555555e-08</v>
       </c>
       <c r="T3" t="b">
         <v>1</v>
@@ -2725,64 +2725,64 @@
       <c r="AN3" t="inlineStr"/>
       <c r="AO3" t="inlineStr"/>
       <c r="AP3" t="n">
-        <v>26593060.94914419</v>
+        <v>53186121.89828838</v>
       </c>
       <c r="AQ3" t="n">
-        <v>26593060.94914419</v>
+        <v>53186121.89828838</v>
       </c>
       <c r="AR3" t="n">
-        <v>26593060.94914419</v>
+        <v>53186121.89828838</v>
       </c>
       <c r="AS3" t="n">
-        <v>26593060.94914419</v>
+        <v>53186121.89828838</v>
       </c>
       <c r="AT3" t="n">
-        <v>26593060.94914419</v>
+        <v>53186121.89828838</v>
       </c>
       <c r="AU3" t="n">
-        <v>33614299.96304332</v>
+        <v>67228599.92608663</v>
       </c>
       <c r="AV3" t="n">
-        <v>33614299.96304332</v>
+        <v>67228599.92608663</v>
       </c>
       <c r="AW3" t="n">
-        <v>33614299.96304332</v>
+        <v>67228599.92608663</v>
       </c>
       <c r="AX3" t="n">
-        <v>33614299.96304332</v>
+        <v>67228599.92608663</v>
       </c>
       <c r="AY3" t="n">
-        <v>33614299.96304332</v>
+        <v>67228599.92608663</v>
       </c>
       <c r="AZ3" t="n">
-        <v>41160186.24828219</v>
+        <v>82320372.49656437</v>
       </c>
       <c r="BA3" t="n">
-        <v>41160186.24828219</v>
+        <v>82320372.49656437</v>
       </c>
       <c r="BB3" t="n">
-        <v>41160186.24828219</v>
+        <v>82320372.49656437</v>
       </c>
       <c r="BC3" t="n">
-        <v>41160186.24828219</v>
+        <v>82320372.49656437</v>
       </c>
       <c r="BD3" t="n">
-        <v>41160186.24828219</v>
+        <v>82320372.49656437</v>
       </c>
       <c r="BE3" t="n">
-        <v>490662076.9442202</v>
+        <v>981324153.8884404</v>
       </c>
       <c r="BF3" t="n">
-        <v>490662076.9442202</v>
+        <v>981324153.8884404</v>
       </c>
       <c r="BG3" t="n">
-        <v>490662076.9442202</v>
+        <v>981324153.8884404</v>
       </c>
       <c r="BH3" t="n">
-        <v>490662076.9442202</v>
+        <v>981324153.8884404</v>
       </c>
       <c r="BI3" t="n">
-        <v>490662076.9442202</v>
+        <v>981324153.8884404</v>
       </c>
       <c r="BJ3" t="n">
         <v>0</v>
@@ -3512,13 +3512,13 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>5.887086984625222e+16</v>
+        <v>1.177417396925044e+17</v>
       </c>
       <c r="E3" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="F3" t="n">
-        <v>3862367099.222991</v>
+        <v>7724734198.445983</v>
       </c>
       <c r="G3" t="n">
         <v>0.08449193122405597</v>
@@ -3534,7 +3534,7 @@
         <v>15</v>
       </c>
       <c r="L3" t="n">
-        <v>500</v>
+        <v>1000</v>
       </c>
       <c r="M3" t="n">
         <v>0.7</v>
@@ -3548,7 +3548,7 @@
         <v>0.4</v>
       </c>
       <c r="P3" t="n">
-        <v>1631193</v>
+        <v>2629180</v>
       </c>
       <c r="Q3" t="n">
         <v>2.778955806943149e+16</v>
@@ -3557,7 +3557,7 @@
         <v>2e+20</v>
       </c>
       <c r="S3" t="n">
-        <v>8.333333333333333e-08</v>
+        <v>4.166666666666666e-08</v>
       </c>
       <c r="T3" t="b">
         <v>1</v>
@@ -3592,64 +3592,64 @@
       <c r="AN3" t="inlineStr"/>
       <c r="AO3" t="inlineStr"/>
       <c r="AP3" t="n">
-        <v>7704424.760277195</v>
+        <v>15408849.52055439</v>
       </c>
       <c r="AQ3" t="n">
-        <v>7704424.760277195</v>
+        <v>15408849.52055439</v>
       </c>
       <c r="AR3" t="n">
-        <v>7704424.760277195</v>
+        <v>15408849.52055439</v>
       </c>
       <c r="AS3" t="n">
-        <v>7704424.760277195</v>
+        <v>15408849.52055439</v>
       </c>
       <c r="AT3" t="n">
-        <v>7704424.760277195</v>
+        <v>15408849.52055439</v>
       </c>
       <c r="AU3" t="n">
-        <v>9563650.930242626</v>
+        <v>19127301.86048525</v>
       </c>
       <c r="AV3" t="n">
-        <v>9563650.930242626</v>
+        <v>19127301.86048525</v>
       </c>
       <c r="AW3" t="n">
-        <v>9563650.930242626</v>
+        <v>19127301.86048525</v>
       </c>
       <c r="AX3" t="n">
-        <v>9563650.930242626</v>
+        <v>19127301.86048525</v>
       </c>
       <c r="AY3" t="n">
-        <v>9563650.930242626</v>
+        <v>19127301.86048525</v>
       </c>
       <c r="AZ3" t="n">
-        <v>5895947.28146222</v>
+        <v>11791894.56292444</v>
       </c>
       <c r="BA3" t="n">
-        <v>5895947.28146222</v>
+        <v>11791894.56292444</v>
       </c>
       <c r="BB3" t="n">
-        <v>5895947.28146222</v>
+        <v>11791894.56292444</v>
       </c>
       <c r="BC3" t="n">
-        <v>5895947.28146222</v>
+        <v>11791894.56292444</v>
       </c>
       <c r="BD3" t="n">
-        <v>5895947.28146222</v>
+        <v>11791894.56292444</v>
       </c>
       <c r="BE3" t="n">
-        <v>274268211.7483228</v>
+        <v>548536423.4966457</v>
       </c>
       <c r="BF3" t="n">
-        <v>274268211.7483228</v>
+        <v>548536423.4966457</v>
       </c>
       <c r="BG3" t="n">
-        <v>274268211.7483228</v>
+        <v>548536423.4966457</v>
       </c>
       <c r="BH3" t="n">
-        <v>274268211.7483228</v>
+        <v>548536423.4966457</v>
       </c>
       <c r="BI3" t="n">
-        <v>274268211.7483228</v>
+        <v>548536423.4966457</v>
       </c>
       <c r="BJ3" t="n">
         <v>0</v>
@@ -6482,13 +6482,13 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>3.896014799106203e+16</v>
+        <v>1.948007399553102e+16</v>
       </c>
       <c r="F12" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G12" t="n">
-        <v>1801958069.217269</v>
+        <v>900979034.6086345</v>
       </c>
       <c r="H12" t="n">
         <v>0.01637572546923326</v>
@@ -6506,7 +6506,7 @@
         <v>10</v>
       </c>
       <c r="M12" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="N12" t="n">
         <v>0.6</v>
@@ -6520,7 +6520,7 @@
         <v>0.3</v>
       </c>
       <c r="Q12" t="n">
-        <v>2191287</v>
+        <v>1193089</v>
       </c>
       <c r="R12" t="n">
         <v>6503081735241510</v>
@@ -6529,7 +6529,7 @@
         <v>1.5e+20</v>
       </c>
       <c r="T12" t="n">
-        <v>2.777777777777778e-08</v>
+        <v>5.555555555555555e-08</v>
       </c>
       <c r="U12" t="b">
         <v>1</v>
@@ -6564,79 +6564,79 @@
       <c r="AO12" t="inlineStr"/>
       <c r="AP12" t="inlineStr"/>
       <c r="AQ12" t="n">
-        <v>3605118.586925264</v>
+        <v>1802559.293462632</v>
       </c>
       <c r="AR12" t="n">
-        <v>3605118.586925264</v>
+        <v>1802559.293462632</v>
       </c>
       <c r="AS12" t="n">
-        <v>3605118.586925264</v>
+        <v>1802559.293462632</v>
       </c>
       <c r="AT12" t="n">
-        <v>3605118.586925264</v>
+        <v>1802559.293462632</v>
       </c>
       <c r="AU12" t="n">
-        <v>3605118.586925264</v>
+        <v>1802559.293462632</v>
       </c>
       <c r="AV12" t="n">
-        <v>4375147.554038037</v>
+        <v>2187573.777019018</v>
       </c>
       <c r="AW12" t="n">
-        <v>4375147.554038037</v>
+        <v>2187573.777019018</v>
       </c>
       <c r="AX12" t="n">
-        <v>4375147.554038037</v>
+        <v>2187573.777019018</v>
       </c>
       <c r="AY12" t="n">
-        <v>4375147.554038037</v>
+        <v>2187573.777019018</v>
       </c>
       <c r="AZ12" t="n">
-        <v>4375147.554038037</v>
+        <v>2187573.777019018</v>
       </c>
       <c r="BA12" t="n">
-        <v>476233.9426265357</v>
+        <v>238116.9713132679</v>
       </c>
       <c r="BB12" t="n">
-        <v>476233.9426265357</v>
+        <v>238116.9713132679</v>
       </c>
       <c r="BC12" t="n">
-        <v>476233.9426265357</v>
+        <v>238116.9713132679</v>
       </c>
       <c r="BD12" t="n">
-        <v>476233.9426265357</v>
+        <v>238116.9713132679</v>
       </c>
       <c r="BE12" t="n">
-        <v>476233.9426265357</v>
+        <v>238116.9713132679</v>
       </c>
       <c r="BF12" t="n">
-        <v>516441161.9396554</v>
+        <v>258220580.9698277</v>
       </c>
       <c r="BG12" t="n">
-        <v>516441161.9396554</v>
+        <v>258220580.9698277</v>
       </c>
       <c r="BH12" t="n">
-        <v>516441161.9396554</v>
+        <v>258220580.9698277</v>
       </c>
       <c r="BI12" t="n">
-        <v>516441161.9396554</v>
+        <v>258220580.9698277</v>
       </c>
       <c r="BJ12" t="n">
-        <v>516441161.9396554</v>
+        <v>258220580.9698277</v>
       </c>
       <c r="BK12" t="n">
-        <v>162076158.2847663</v>
+        <v>81038079.14238313</v>
       </c>
       <c r="BL12" t="n">
-        <v>162076158.2847663</v>
+        <v>81038079.14238313</v>
       </c>
       <c r="BM12" t="n">
-        <v>162076158.2847663</v>
+        <v>81038079.14238313</v>
       </c>
       <c r="BN12" t="n">
-        <v>162076158.2847663</v>
+        <v>81038079.14238313</v>
       </c>
       <c r="BO12" t="n">
-        <v>162076158.2847663</v>
+        <v>81038079.14238313</v>
       </c>
       <c r="BP12" t="inlineStr"/>
       <c r="BQ12" t="inlineStr"/>
@@ -7354,13 +7354,13 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>2.884764946099001e+16</v>
+        <v>5.769529892198002e+16</v>
       </c>
       <c r="F16" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="G16" t="n">
-        <v>12207378845.11138</v>
+        <v>24414757690.22276</v>
       </c>
       <c r="H16" t="n">
         <v>0.2067897919490654</v>
@@ -7376,7 +7376,7 @@
         <v>20</v>
       </c>
       <c r="M16" t="n">
-        <v>1000</v>
+        <v>2000</v>
       </c>
       <c r="N16" t="n">
         <v>0.7</v>
@@ -7390,7 +7390,7 @@
         <v>0.3</v>
       </c>
       <c r="Q16" t="n">
-        <v>2981040</v>
+        <v>4976946</v>
       </c>
       <c r="R16" t="n">
         <v>4.79379534335385e+16</v>
@@ -7399,7 +7399,7 @@
         <v>2e+20</v>
       </c>
       <c r="T16" t="n">
-        <v>1.111111111111111e-07</v>
+        <v>5.555555555555555e-08</v>
       </c>
       <c r="U16" t="b">
         <v>1</v>
@@ -7434,64 +7434,64 @@
       <c r="AO16" t="inlineStr"/>
       <c r="AP16" t="inlineStr"/>
       <c r="AQ16" t="n">
-        <v>26593060.94914419</v>
+        <v>53186121.89828838</v>
       </c>
       <c r="AR16" t="n">
-        <v>26593060.94914419</v>
+        <v>53186121.89828838</v>
       </c>
       <c r="AS16" t="n">
-        <v>26593060.94914419</v>
+        <v>53186121.89828838</v>
       </c>
       <c r="AT16" t="n">
-        <v>26593060.94914419</v>
+        <v>53186121.89828838</v>
       </c>
       <c r="AU16" t="n">
-        <v>26593060.94914419</v>
+        <v>53186121.89828838</v>
       </c>
       <c r="AV16" t="n">
-        <v>33614299.96304332</v>
+        <v>67228599.92608663</v>
       </c>
       <c r="AW16" t="n">
-        <v>33614299.96304332</v>
+        <v>67228599.92608663</v>
       </c>
       <c r="AX16" t="n">
-        <v>33614299.96304332</v>
+        <v>67228599.92608663</v>
       </c>
       <c r="AY16" t="n">
-        <v>33614299.96304332</v>
+        <v>67228599.92608663</v>
       </c>
       <c r="AZ16" t="n">
-        <v>33614299.96304332</v>
+        <v>67228599.92608663</v>
       </c>
       <c r="BA16" t="n">
-        <v>41160186.24828219</v>
+        <v>82320372.49656437</v>
       </c>
       <c r="BB16" t="n">
-        <v>41160186.24828219</v>
+        <v>82320372.49656437</v>
       </c>
       <c r="BC16" t="n">
-        <v>41160186.24828219</v>
+        <v>82320372.49656437</v>
       </c>
       <c r="BD16" t="n">
-        <v>41160186.24828219</v>
+        <v>82320372.49656437</v>
       </c>
       <c r="BE16" t="n">
-        <v>41160186.24828219</v>
+        <v>82320372.49656437</v>
       </c>
       <c r="BF16" t="n">
-        <v>490662076.9442202</v>
+        <v>981324153.8884404</v>
       </c>
       <c r="BG16" t="n">
-        <v>490662076.9442202</v>
+        <v>981324153.8884404</v>
       </c>
       <c r="BH16" t="n">
-        <v>490662076.9442202</v>
+        <v>981324153.8884404</v>
       </c>
       <c r="BI16" t="n">
-        <v>490662076.9442202</v>
+        <v>981324153.8884404</v>
       </c>
       <c r="BJ16" t="n">
-        <v>490662076.9442202</v>
+        <v>981324153.8884404</v>
       </c>
       <c r="BK16" t="n">
         <v>0</v>
@@ -7562,13 +7562,13 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>5.887086984625222e+16</v>
+        <v>1.177417396925044e+17</v>
       </c>
       <c r="F17" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="G17" t="n">
-        <v>3862367099.222991</v>
+        <v>7724734198.445983</v>
       </c>
       <c r="H17" t="n">
         <v>0.08449193122405597</v>
@@ -7584,7 +7584,7 @@
         <v>15</v>
       </c>
       <c r="M17" t="n">
-        <v>500</v>
+        <v>1000</v>
       </c>
       <c r="N17" t="n">
         <v>0.7</v>
@@ -7598,7 +7598,7 @@
         <v>0.4</v>
       </c>
       <c r="Q17" t="n">
-        <v>1631193</v>
+        <v>2629180</v>
       </c>
       <c r="R17" t="n">
         <v>2.778955806943149e+16</v>
@@ -7607,7 +7607,7 @@
         <v>2e+20</v>
       </c>
       <c r="T17" t="n">
-        <v>8.333333333333333e-08</v>
+        <v>4.166666666666666e-08</v>
       </c>
       <c r="U17" t="b">
         <v>1</v>
@@ -7642,64 +7642,64 @@
       <c r="AO17" t="inlineStr"/>
       <c r="AP17" t="inlineStr"/>
       <c r="AQ17" t="n">
-        <v>7704424.760277195</v>
+        <v>15408849.52055439</v>
       </c>
       <c r="AR17" t="n">
-        <v>7704424.760277195</v>
+        <v>15408849.52055439</v>
       </c>
       <c r="AS17" t="n">
-        <v>7704424.760277195</v>
+        <v>15408849.52055439</v>
       </c>
       <c r="AT17" t="n">
-        <v>7704424.760277195</v>
+        <v>15408849.52055439</v>
       </c>
       <c r="AU17" t="n">
-        <v>7704424.760277195</v>
+        <v>15408849.52055439</v>
       </c>
       <c r="AV17" t="n">
-        <v>9563650.930242626</v>
+        <v>19127301.86048525</v>
       </c>
       <c r="AW17" t="n">
-        <v>9563650.930242626</v>
+        <v>19127301.86048525</v>
       </c>
       <c r="AX17" t="n">
-        <v>9563650.930242626</v>
+        <v>19127301.86048525</v>
       </c>
       <c r="AY17" t="n">
-        <v>9563650.930242626</v>
+        <v>19127301.86048525</v>
       </c>
       <c r="AZ17" t="n">
-        <v>9563650.930242626</v>
+        <v>19127301.86048525</v>
       </c>
       <c r="BA17" t="n">
-        <v>5895947.28146222</v>
+        <v>11791894.56292444</v>
       </c>
       <c r="BB17" t="n">
-        <v>5895947.28146222</v>
+        <v>11791894.56292444</v>
       </c>
       <c r="BC17" t="n">
-        <v>5895947.28146222</v>
+        <v>11791894.56292444</v>
       </c>
       <c r="BD17" t="n">
-        <v>5895947.28146222</v>
+        <v>11791894.56292444</v>
       </c>
       <c r="BE17" t="n">
-        <v>5895947.28146222</v>
+        <v>11791894.56292444</v>
       </c>
       <c r="BF17" t="n">
-        <v>274268211.7483228</v>
+        <v>548536423.4966457</v>
       </c>
       <c r="BG17" t="n">
-        <v>274268211.7483228</v>
+        <v>548536423.4966457</v>
       </c>
       <c r="BH17" t="n">
-        <v>274268211.7483228</v>
+        <v>548536423.4966457</v>
       </c>
       <c r="BI17" t="n">
-        <v>274268211.7483228</v>
+        <v>548536423.4966457</v>
       </c>
       <c r="BJ17" t="n">
-        <v>274268211.7483228</v>
+        <v>548536423.4966457</v>
       </c>
       <c r="BK17" t="n">
         <v>0</v>
@@ -11156,13 +11156,13 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>3.896014799106203e+16</v>
+        <v>1.948007399553102e+16</v>
       </c>
       <c r="E5" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F5" t="n">
-        <v>1801958069.217269</v>
+        <v>900979034.6086345</v>
       </c>
       <c r="G5" t="n">
         <v>0.01637572546923326</v>
@@ -11180,7 +11180,7 @@
         <v>10</v>
       </c>
       <c r="L5" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="M5" t="n">
         <v>0.6</v>
@@ -11194,7 +11194,7 @@
         <v>0.3</v>
       </c>
       <c r="P5" t="n">
-        <v>2191287</v>
+        <v>1193089</v>
       </c>
       <c r="Q5" t="n">
         <v>6503081735241510</v>
@@ -11203,7 +11203,7 @@
         <v>1.5e+20</v>
       </c>
       <c r="S5" t="n">
-        <v>2.777777777777778e-08</v>
+        <v>5.555555555555555e-08</v>
       </c>
       <c r="T5" t="b">
         <v>1</v>
@@ -11238,79 +11238,79 @@
       <c r="AN5" t="inlineStr"/>
       <c r="AO5" t="inlineStr"/>
       <c r="AP5" t="n">
-        <v>3605118.586925264</v>
+        <v>1802559.293462632</v>
       </c>
       <c r="AQ5" t="n">
-        <v>3605118.586925264</v>
+        <v>1802559.293462632</v>
       </c>
       <c r="AR5" t="n">
-        <v>3605118.586925264</v>
+        <v>1802559.293462632</v>
       </c>
       <c r="AS5" t="n">
-        <v>3605118.586925264</v>
+        <v>1802559.293462632</v>
       </c>
       <c r="AT5" t="n">
-        <v>3605118.586925264</v>
+        <v>1802559.293462632</v>
       </c>
       <c r="AU5" t="n">
-        <v>4375147.554038037</v>
+        <v>2187573.777019018</v>
       </c>
       <c r="AV5" t="n">
-        <v>4375147.554038037</v>
+        <v>2187573.777019018</v>
       </c>
       <c r="AW5" t="n">
-        <v>4375147.554038037</v>
+        <v>2187573.777019018</v>
       </c>
       <c r="AX5" t="n">
-        <v>4375147.554038037</v>
+        <v>2187573.777019018</v>
       </c>
       <c r="AY5" t="n">
-        <v>4375147.554038037</v>
+        <v>2187573.777019018</v>
       </c>
       <c r="AZ5" t="n">
-        <v>476233.9426265357</v>
+        <v>238116.9713132679</v>
       </c>
       <c r="BA5" t="n">
-        <v>476233.9426265357</v>
+        <v>238116.9713132679</v>
       </c>
       <c r="BB5" t="n">
-        <v>476233.9426265357</v>
+        <v>238116.9713132679</v>
       </c>
       <c r="BC5" t="n">
-        <v>476233.9426265357</v>
+        <v>238116.9713132679</v>
       </c>
       <c r="BD5" t="n">
-        <v>476233.9426265357</v>
+        <v>238116.9713132679</v>
       </c>
       <c r="BE5" t="n">
-        <v>516441161.9396554</v>
+        <v>258220580.9698277</v>
       </c>
       <c r="BF5" t="n">
-        <v>516441161.9396554</v>
+        <v>258220580.9698277</v>
       </c>
       <c r="BG5" t="n">
-        <v>516441161.9396554</v>
+        <v>258220580.9698277</v>
       </c>
       <c r="BH5" t="n">
-        <v>516441161.9396554</v>
+        <v>258220580.9698277</v>
       </c>
       <c r="BI5" t="n">
-        <v>516441161.9396554</v>
+        <v>258220580.9698277</v>
       </c>
       <c r="BJ5" t="n">
-        <v>162076158.2847663</v>
+        <v>81038079.14238313</v>
       </c>
       <c r="BK5" t="n">
-        <v>162076158.2847663</v>
+        <v>81038079.14238313</v>
       </c>
       <c r="BL5" t="n">
-        <v>162076158.2847663</v>
+        <v>81038079.14238313</v>
       </c>
       <c r="BM5" t="n">
-        <v>162076158.2847663</v>
+        <v>81038079.14238313</v>
       </c>
       <c r="BN5" t="n">
-        <v>162076158.2847663</v>
+        <v>81038079.14238313</v>
       </c>
       <c r="BO5" t="inlineStr"/>
       <c r="BP5" t="inlineStr"/>
@@ -11775,13 +11775,13 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>2.884764946099001e+16</v>
+        <v>5.769529892198002e+16</v>
       </c>
       <c r="E8" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="F8" t="n">
-        <v>12207378845.11138</v>
+        <v>24414757690.22276</v>
       </c>
       <c r="G8" t="n">
         <v>0.2067897919490654</v>
@@ -11797,7 +11797,7 @@
         <v>20</v>
       </c>
       <c r="L8" t="n">
-        <v>1000</v>
+        <v>2000</v>
       </c>
       <c r="M8" t="n">
         <v>0.7</v>
@@ -11811,7 +11811,7 @@
         <v>0.3</v>
       </c>
       <c r="P8" t="n">
-        <v>2981040</v>
+        <v>4976946</v>
       </c>
       <c r="Q8" t="n">
         <v>4.79379534335385e+16</v>
@@ -11820,7 +11820,7 @@
         <v>2e+20</v>
       </c>
       <c r="S8" t="n">
-        <v>1.111111111111111e-07</v>
+        <v>5.555555555555555e-08</v>
       </c>
       <c r="T8" t="b">
         <v>1</v>
@@ -11855,64 +11855,64 @@
       <c r="AN8" t="inlineStr"/>
       <c r="AO8" t="inlineStr"/>
       <c r="AP8" t="n">
-        <v>26593060.94914419</v>
+        <v>53186121.89828838</v>
       </c>
       <c r="AQ8" t="n">
-        <v>26593060.94914419</v>
+        <v>53186121.89828838</v>
       </c>
       <c r="AR8" t="n">
-        <v>26593060.94914419</v>
+        <v>53186121.89828838</v>
       </c>
       <c r="AS8" t="n">
-        <v>26593060.94914419</v>
+        <v>53186121.89828838</v>
       </c>
       <c r="AT8" t="n">
-        <v>26593060.94914419</v>
+        <v>53186121.89828838</v>
       </c>
       <c r="AU8" t="n">
-        <v>33614299.96304332</v>
+        <v>67228599.92608663</v>
       </c>
       <c r="AV8" t="n">
-        <v>33614299.96304332</v>
+        <v>67228599.92608663</v>
       </c>
       <c r="AW8" t="n">
-        <v>33614299.96304332</v>
+        <v>67228599.92608663</v>
       </c>
       <c r="AX8" t="n">
-        <v>33614299.96304332</v>
+        <v>67228599.92608663</v>
       </c>
       <c r="AY8" t="n">
-        <v>33614299.96304332</v>
+        <v>67228599.92608663</v>
       </c>
       <c r="AZ8" t="n">
-        <v>41160186.24828219</v>
+        <v>82320372.49656437</v>
       </c>
       <c r="BA8" t="n">
-        <v>41160186.24828219</v>
+        <v>82320372.49656437</v>
       </c>
       <c r="BB8" t="n">
-        <v>41160186.24828219</v>
+        <v>82320372.49656437</v>
       </c>
       <c r="BC8" t="n">
-        <v>41160186.24828219</v>
+        <v>82320372.49656437</v>
       </c>
       <c r="BD8" t="n">
-        <v>41160186.24828219</v>
+        <v>82320372.49656437</v>
       </c>
       <c r="BE8" t="n">
-        <v>490662076.9442202</v>
+        <v>981324153.8884404</v>
       </c>
       <c r="BF8" t="n">
-        <v>490662076.9442202</v>
+        <v>981324153.8884404</v>
       </c>
       <c r="BG8" t="n">
-        <v>490662076.9442202</v>
+        <v>981324153.8884404</v>
       </c>
       <c r="BH8" t="n">
-        <v>490662076.9442202</v>
+        <v>981324153.8884404</v>
       </c>
       <c r="BI8" t="n">
-        <v>490662076.9442202</v>
+        <v>981324153.8884404</v>
       </c>
       <c r="BJ8" t="n">
         <v>0</v>
@@ -11980,13 +11980,13 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>5.887086984625222e+16</v>
+        <v>1.177417396925044e+17</v>
       </c>
       <c r="E9" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="F9" t="n">
-        <v>3862367099.222991</v>
+        <v>7724734198.445983</v>
       </c>
       <c r="G9" t="n">
         <v>0.08449193122405597</v>
@@ -12002,7 +12002,7 @@
         <v>15</v>
       </c>
       <c r="L9" t="n">
-        <v>500</v>
+        <v>1000</v>
       </c>
       <c r="M9" t="n">
         <v>0.7</v>
@@ -12016,7 +12016,7 @@
         <v>0.4</v>
       </c>
       <c r="P9" t="n">
-        <v>1631193</v>
+        <v>2629180</v>
       </c>
       <c r="Q9" t="n">
         <v>2.778955806943149e+16</v>
@@ -12025,7 +12025,7 @@
         <v>2e+20</v>
       </c>
       <c r="S9" t="n">
-        <v>8.333333333333333e-08</v>
+        <v>4.166666666666666e-08</v>
       </c>
       <c r="T9" t="b">
         <v>1</v>
@@ -12060,64 +12060,64 @@
       <c r="AN9" t="inlineStr"/>
       <c r="AO9" t="inlineStr"/>
       <c r="AP9" t="n">
-        <v>7704424.760277195</v>
+        <v>15408849.52055439</v>
       </c>
       <c r="AQ9" t="n">
-        <v>7704424.760277195</v>
+        <v>15408849.52055439</v>
       </c>
       <c r="AR9" t="n">
-        <v>7704424.760277195</v>
+        <v>15408849.52055439</v>
       </c>
       <c r="AS9" t="n">
-        <v>7704424.760277195</v>
+        <v>15408849.52055439</v>
       </c>
       <c r="AT9" t="n">
-        <v>7704424.760277195</v>
+        <v>15408849.52055439</v>
       </c>
       <c r="AU9" t="n">
-        <v>9563650.930242626</v>
+        <v>19127301.86048525</v>
       </c>
       <c r="AV9" t="n">
-        <v>9563650.930242626</v>
+        <v>19127301.86048525</v>
       </c>
       <c r="AW9" t="n">
-        <v>9563650.930242626</v>
+        <v>19127301.86048525</v>
       </c>
       <c r="AX9" t="n">
-        <v>9563650.930242626</v>
+        <v>19127301.86048525</v>
       </c>
       <c r="AY9" t="n">
-        <v>9563650.930242626</v>
+        <v>19127301.86048525</v>
       </c>
       <c r="AZ9" t="n">
-        <v>5895947.28146222</v>
+        <v>11791894.56292444</v>
       </c>
       <c r="BA9" t="n">
-        <v>5895947.28146222</v>
+        <v>11791894.56292444</v>
       </c>
       <c r="BB9" t="n">
-        <v>5895947.28146222</v>
+        <v>11791894.56292444</v>
       </c>
       <c r="BC9" t="n">
-        <v>5895947.28146222</v>
+        <v>11791894.56292444</v>
       </c>
       <c r="BD9" t="n">
-        <v>5895947.28146222</v>
+        <v>11791894.56292444</v>
       </c>
       <c r="BE9" t="n">
-        <v>274268211.7483228</v>
+        <v>548536423.4966457</v>
       </c>
       <c r="BF9" t="n">
-        <v>274268211.7483228</v>
+        <v>548536423.4966457</v>
       </c>
       <c r="BG9" t="n">
-        <v>274268211.7483228</v>
+        <v>548536423.4966457</v>
       </c>
       <c r="BH9" t="n">
-        <v>274268211.7483228</v>
+        <v>548536423.4966457</v>
       </c>
       <c r="BI9" t="n">
-        <v>274268211.7483228</v>
+        <v>548536423.4966457</v>
       </c>
       <c r="BJ9" t="n">
         <v>0</v>
@@ -15450,13 +15450,13 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>3.896014799106203e+16</v>
+        <v>1.948007399553102e+16</v>
       </c>
       <c r="E3" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F3" t="n">
-        <v>1801958069.217269</v>
+        <v>900979034.6086345</v>
       </c>
       <c r="G3" t="n">
         <v>0.01637572546923326</v>
@@ -15474,7 +15474,7 @@
         <v>10</v>
       </c>
       <c r="L3" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="M3" t="n">
         <v>0.6</v>
@@ -15488,7 +15488,7 @@
         <v>0.3</v>
       </c>
       <c r="P3" t="n">
-        <v>2191287</v>
+        <v>1193089</v>
       </c>
       <c r="Q3" t="n">
         <v>6503081735241510</v>
@@ -15497,7 +15497,7 @@
         <v>1.5e+20</v>
       </c>
       <c r="S3" t="n">
-        <v>2.777777777777778e-08</v>
+        <v>5.555555555555555e-08</v>
       </c>
       <c r="T3" t="b">
         <v>1</v>
@@ -15515,6 +15515,875 @@
       </c>
       <c r="Z3" t="n">
         <v>1082226333.085056</v>
+      </c>
+      <c r="AA3" t="inlineStr"/>
+      <c r="AB3" t="inlineStr"/>
+      <c r="AC3" t="inlineStr"/>
+      <c r="AD3" t="inlineStr"/>
+      <c r="AE3" t="inlineStr"/>
+      <c r="AF3" t="inlineStr"/>
+      <c r="AG3" t="inlineStr"/>
+      <c r="AH3" t="inlineStr"/>
+      <c r="AI3" t="inlineStr"/>
+      <c r="AJ3" t="inlineStr"/>
+      <c r="AK3" t="inlineStr"/>
+      <c r="AL3" t="inlineStr"/>
+      <c r="AM3" t="inlineStr"/>
+      <c r="AN3" t="inlineStr"/>
+      <c r="AO3" t="inlineStr"/>
+      <c r="AP3" t="n">
+        <v>1802559.293462632</v>
+      </c>
+      <c r="AQ3" t="n">
+        <v>1802559.293462632</v>
+      </c>
+      <c r="AR3" t="n">
+        <v>1802559.293462632</v>
+      </c>
+      <c r="AS3" t="n">
+        <v>1802559.293462632</v>
+      </c>
+      <c r="AT3" t="n">
+        <v>1802559.293462632</v>
+      </c>
+      <c r="AU3" t="n">
+        <v>2187573.777019018</v>
+      </c>
+      <c r="AV3" t="n">
+        <v>2187573.777019018</v>
+      </c>
+      <c r="AW3" t="n">
+        <v>2187573.777019018</v>
+      </c>
+      <c r="AX3" t="n">
+        <v>2187573.777019018</v>
+      </c>
+      <c r="AY3" t="n">
+        <v>2187573.777019018</v>
+      </c>
+      <c r="AZ3" t="n">
+        <v>238116.9713132679</v>
+      </c>
+      <c r="BA3" t="n">
+        <v>238116.9713132679</v>
+      </c>
+      <c r="BB3" t="n">
+        <v>238116.9713132679</v>
+      </c>
+      <c r="BC3" t="n">
+        <v>238116.9713132679</v>
+      </c>
+      <c r="BD3" t="n">
+        <v>238116.9713132679</v>
+      </c>
+      <c r="BE3" t="n">
+        <v>258220580.9698277</v>
+      </c>
+      <c r="BF3" t="n">
+        <v>258220580.9698277</v>
+      </c>
+      <c r="BG3" t="n">
+        <v>258220580.9698277</v>
+      </c>
+      <c r="BH3" t="n">
+        <v>258220580.9698277</v>
+      </c>
+      <c r="BI3" t="n">
+        <v>258220580.9698277</v>
+      </c>
+      <c r="BJ3" t="n">
+        <v>81038079.14238313</v>
+      </c>
+      <c r="BK3" t="n">
+        <v>81038079.14238313</v>
+      </c>
+      <c r="BL3" t="n">
+        <v>81038079.14238313</v>
+      </c>
+      <c r="BM3" t="n">
+        <v>81038079.14238313</v>
+      </c>
+      <c r="BN3" t="n">
+        <v>81038079.14238313</v>
+      </c>
+      <c r="BO3" t="inlineStr"/>
+      <c r="BP3" t="inlineStr"/>
+      <c r="BQ3" t="inlineStr"/>
+      <c r="BR3" t="inlineStr"/>
+      <c r="BS3" t="inlineStr"/>
+      <c r="BT3" t="n">
+        <v>1.5e+20</v>
+      </c>
+      <c r="BU3" t="n">
+        <v>1.5e+20</v>
+      </c>
+      <c r="BV3" t="n">
+        <v>1.5e+20</v>
+      </c>
+      <c r="BW3" t="n">
+        <v>1.5e+20</v>
+      </c>
+      <c r="BX3" t="n">
+        <v>1.5e+20</v>
+      </c>
+      <c r="BY3" t="n">
+        <v>9910759386455950</v>
+      </c>
+      <c r="BZ3" t="n">
+        <v>9910759386455950</v>
+      </c>
+      <c r="CA3" t="n">
+        <v>9910759386455950</v>
+      </c>
+      <c r="CB3" t="n">
+        <v>9910759386455950</v>
+      </c>
+      <c r="CC3" t="n">
+        <v>9910759386455950</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:CC3"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Strategy</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Rank_in_Strategy</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Source_File</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>E_lost</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>I_target</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>P_DT_eq</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Q_DD</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Q_DT_eq</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>TBR_DDn</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>TBR_DT</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>T_i</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>V_plasma</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>capacity_factor</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>error</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>eta_th</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>linear_index</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>n_He3</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>n_tot</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>price_of_electricity</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>sol_success</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>t_startup</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>tau_ifc</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>tau_ofc</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>tau_p_He3</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>tau_p_T</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>unrealized_profits</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>N_ifc_t0</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>N_ifc_t25</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>N_ifc_t50</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>N_ifc_t75</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>N_ifc_t100</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>N_ofc_t0</t>
+        </is>
+      </c>
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
+          <t>N_ofc_t25</t>
+        </is>
+      </c>
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
+          <t>N_ofc_t50</t>
+        </is>
+      </c>
+      <c r="AI1" s="1" t="inlineStr">
+        <is>
+          <t>N_ofc_t75</t>
+        </is>
+      </c>
+      <c r="AJ1" s="1" t="inlineStr">
+        <is>
+          <t>N_ofc_t100</t>
+        </is>
+      </c>
+      <c r="AK1" s="1" t="inlineStr">
+        <is>
+          <t>N_stor_t0</t>
+        </is>
+      </c>
+      <c r="AL1" s="1" t="inlineStr">
+        <is>
+          <t>N_stor_t25</t>
+        </is>
+      </c>
+      <c r="AM1" s="1" t="inlineStr">
+        <is>
+          <t>N_stor_t50</t>
+        </is>
+      </c>
+      <c r="AN1" s="1" t="inlineStr">
+        <is>
+          <t>N_stor_t75</t>
+        </is>
+      </c>
+      <c r="AO1" s="1" t="inlineStr">
+        <is>
+          <t>N_stor_t100</t>
+        </is>
+      </c>
+      <c r="AP1" s="1" t="inlineStr">
+        <is>
+          <t>P_DDn_t0</t>
+        </is>
+      </c>
+      <c r="AQ1" s="1" t="inlineStr">
+        <is>
+          <t>P_DDn_t25</t>
+        </is>
+      </c>
+      <c r="AR1" s="1" t="inlineStr">
+        <is>
+          <t>P_DDn_t50</t>
+        </is>
+      </c>
+      <c r="AS1" s="1" t="inlineStr">
+        <is>
+          <t>P_DDn_t75</t>
+        </is>
+      </c>
+      <c r="AT1" s="1" t="inlineStr">
+        <is>
+          <t>P_DDn_t100</t>
+        </is>
+      </c>
+      <c r="AU1" s="1" t="inlineStr">
+        <is>
+          <t>P_DDp_t0</t>
+        </is>
+      </c>
+      <c r="AV1" s="1" t="inlineStr">
+        <is>
+          <t>P_DDp_t25</t>
+        </is>
+      </c>
+      <c r="AW1" s="1" t="inlineStr">
+        <is>
+          <t>P_DDp_t50</t>
+        </is>
+      </c>
+      <c r="AX1" s="1" t="inlineStr">
+        <is>
+          <t>P_DDp_t75</t>
+        </is>
+      </c>
+      <c r="AY1" s="1" t="inlineStr">
+        <is>
+          <t>P_DDp_t100</t>
+        </is>
+      </c>
+      <c r="AZ1" s="1" t="inlineStr">
+        <is>
+          <t>P_DT_t0</t>
+        </is>
+      </c>
+      <c r="BA1" s="1" t="inlineStr">
+        <is>
+          <t>P_DT_t25</t>
+        </is>
+      </c>
+      <c r="BB1" s="1" t="inlineStr">
+        <is>
+          <t>P_DT_t50</t>
+        </is>
+      </c>
+      <c r="BC1" s="1" t="inlineStr">
+        <is>
+          <t>P_DT_t75</t>
+        </is>
+      </c>
+      <c r="BD1" s="1" t="inlineStr">
+        <is>
+          <t>P_DT_t100</t>
+        </is>
+      </c>
+      <c r="BE1" s="1" t="inlineStr">
+        <is>
+          <t>P_aux_t0</t>
+        </is>
+      </c>
+      <c r="BF1" s="1" t="inlineStr">
+        <is>
+          <t>P_aux_t25</t>
+        </is>
+      </c>
+      <c r="BG1" s="1" t="inlineStr">
+        <is>
+          <t>P_aux_t50</t>
+        </is>
+      </c>
+      <c r="BH1" s="1" t="inlineStr">
+        <is>
+          <t>P_aux_t75</t>
+        </is>
+      </c>
+      <c r="BI1" s="1" t="inlineStr">
+        <is>
+          <t>P_aux_t100</t>
+        </is>
+      </c>
+      <c r="BJ1" s="1" t="inlineStr">
+        <is>
+          <t>P_aux_DT_eq_t0</t>
+        </is>
+      </c>
+      <c r="BK1" s="1" t="inlineStr">
+        <is>
+          <t>P_aux_DT_eq_t25</t>
+        </is>
+      </c>
+      <c r="BL1" s="1" t="inlineStr">
+        <is>
+          <t>P_aux_DT_eq_t50</t>
+        </is>
+      </c>
+      <c r="BM1" s="1" t="inlineStr">
+        <is>
+          <t>P_aux_DT_eq_t75</t>
+        </is>
+      </c>
+      <c r="BN1" s="1" t="inlineStr">
+        <is>
+          <t>P_aux_DT_eq_t100</t>
+        </is>
+      </c>
+      <c r="BO1" s="1" t="inlineStr">
+        <is>
+          <t>TBE_t0</t>
+        </is>
+      </c>
+      <c r="BP1" s="1" t="inlineStr">
+        <is>
+          <t>TBE_t25</t>
+        </is>
+      </c>
+      <c r="BQ1" s="1" t="inlineStr">
+        <is>
+          <t>TBE_t50</t>
+        </is>
+      </c>
+      <c r="BR1" s="1" t="inlineStr">
+        <is>
+          <t>TBE_t75</t>
+        </is>
+      </c>
+      <c r="BS1" s="1" t="inlineStr">
+        <is>
+          <t>TBE_t100</t>
+        </is>
+      </c>
+      <c r="BT1" s="1" t="inlineStr">
+        <is>
+          <t>n_D_t0</t>
+        </is>
+      </c>
+      <c r="BU1" s="1" t="inlineStr">
+        <is>
+          <t>n_D_t25</t>
+        </is>
+      </c>
+      <c r="BV1" s="1" t="inlineStr">
+        <is>
+          <t>n_D_t50</t>
+        </is>
+      </c>
+      <c r="BW1" s="1" t="inlineStr">
+        <is>
+          <t>n_D_t75</t>
+        </is>
+      </c>
+      <c r="BX1" s="1" t="inlineStr">
+        <is>
+          <t>n_D_t100</t>
+        </is>
+      </c>
+      <c r="BY1" s="1" t="inlineStr">
+        <is>
+          <t>n_T_t0</t>
+        </is>
+      </c>
+      <c r="BZ1" s="1" t="inlineStr">
+        <is>
+          <t>n_T_t25</t>
+        </is>
+      </c>
+      <c r="CA1" s="1" t="inlineStr">
+        <is>
+          <t>n_T_t50</t>
+        </is>
+      </c>
+      <c r="CB1" s="1" t="inlineStr">
+        <is>
+          <t>n_T_t75</t>
+        </is>
+      </c>
+      <c r="CC1" s="1" t="inlineStr">
+        <is>
+          <t>n_T_t100</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Q3_Best</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>ddstartup_20251113_002935_parametric_T_seeded</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>7826287446143086</v>
+      </c>
+      <c r="E2" t="inlineStr"/>
+      <c r="F2" t="n">
+        <v>3603916138.434538</v>
+      </c>
+      <c r="G2" t="n">
+        <v>5.127455749410214</v>
+      </c>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J2" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="K2" t="n">
+        <v>10</v>
+      </c>
+      <c r="L2" t="n">
+        <v>2000</v>
+      </c>
+      <c r="M2" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>b''</t>
+        </is>
+      </c>
+      <c r="O2" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="P2" t="n">
+        <v>5295627</v>
+      </c>
+      <c r="Q2" t="inlineStr"/>
+      <c r="R2" t="n">
+        <v>1.5e+20</v>
+      </c>
+      <c r="S2" t="n">
+        <v>4.166666666666666e-08</v>
+      </c>
+      <c r="T2" t="b">
+        <v>1</v>
+      </c>
+      <c r="U2" t="n">
+        <v>8906643.306762496</v>
+      </c>
+      <c r="V2" t="n">
+        <v>28800</v>
+      </c>
+      <c r="W2" t="n">
+        <v>7200</v>
+      </c>
+      <c r="X2" t="inlineStr"/>
+      <c r="Y2" t="n">
+        <v>5</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>326095310.2559619</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>100</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>6.891318357029416e+25</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>2.194711298264947e+26</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>5.048147762371376e+26</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>9.007116213336876e+26</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>100</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>1.546425121460363e+24</v>
+      </c>
+      <c r="AH2" t="n">
+        <v>4.438176094912333e+24</v>
+      </c>
+      <c r="AI2" t="n">
+        <v>8.453174156956428e+24</v>
+      </c>
+      <c r="AJ2" t="n">
+        <v>1.059389795306354e+25</v>
+      </c>
+      <c r="AK2" t="n">
+        <v>100</v>
+      </c>
+      <c r="AL2" t="n">
+        <v>1.996731041002841e+23</v>
+      </c>
+      <c r="AM2" t="n">
+        <v>1.996731041002841e+23</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>1.996731041002841e+23</v>
+      </c>
+      <c r="AO2" t="n">
+        <v>1.99697192644861e+23</v>
+      </c>
+      <c r="AP2" t="n">
+        <v>7210237.173850519</v>
+      </c>
+      <c r="AQ2" t="n">
+        <v>6685847.562828113</v>
+      </c>
+      <c r="AR2" t="n">
+        <v>5605200.967600255</v>
+      </c>
+      <c r="AS2" t="n">
+        <v>3787102.586796727</v>
+      </c>
+      <c r="AT2" t="n">
+        <v>1802559.293462631</v>
+      </c>
+      <c r="AU2" t="n">
+        <v>8750295.108076064</v>
+      </c>
+      <c r="AV2" t="n">
+        <v>8113899.419915252</v>
+      </c>
+      <c r="AW2" t="n">
+        <v>6802434.014855414</v>
+      </c>
+      <c r="AX2" t="n">
+        <v>4596002.106451184</v>
+      </c>
+      <c r="AY2" t="n">
+        <v>2187573.777019018</v>
+      </c>
+      <c r="AZ2" t="n">
+        <v>9.610443035825428e-06</v>
+      </c>
+      <c r="BA2" t="n">
+        <v>514320168.3826579</v>
+      </c>
+      <c r="BB2" t="n">
+        <v>1503627967.795042</v>
+      </c>
+      <c r="BC2" t="n">
+        <v>2875846322.130662</v>
+      </c>
+      <c r="BD2" t="n">
+        <v>3603916138.434538</v>
+      </c>
+      <c r="BE2" t="n">
+        <v>360081764.4814911</v>
+      </c>
+      <c r="BF2" t="n">
+        <v>359534221.9847848</v>
+      </c>
+      <c r="BG2" t="n">
+        <v>359489793.3288961</v>
+      </c>
+      <c r="BH2" t="n">
+        <v>358947823.0921111</v>
+      </c>
+      <c r="BI2" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ2" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK2" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL2" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM2" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN2" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO2" t="inlineStr"/>
+      <c r="BP2" t="n">
+        <v>3.811278954004925e-05</v>
+      </c>
+      <c r="BQ2" t="n">
+        <v>3.498665693746704e-05</v>
+      </c>
+      <c r="BR2" t="n">
+        <v>2.909196494747936e-05</v>
+      </c>
+      <c r="BS2" t="n">
+        <v>2.043284501928585e-05</v>
+      </c>
+      <c r="BT2" t="n">
+        <v>1.499999999999999e+20</v>
+      </c>
+      <c r="BU2" t="n">
+        <v>1.444424076740985e+20</v>
+      </c>
+      <c r="BV2" t="n">
+        <v>1.322549933103414e+20</v>
+      </c>
+      <c r="BW2" t="n">
+        <v>1.087101308669026e+20</v>
+      </c>
+      <c r="BX2" t="n">
+        <v>7.499999999999998e+19</v>
+      </c>
+      <c r="BY2" t="n">
+        <v>100000</v>
+      </c>
+      <c r="BZ2" t="n">
+        <v>5.557592325901557e+18</v>
+      </c>
+      <c r="CA2" t="n">
+        <v>1.774500668965863e+19</v>
+      </c>
+      <c r="CB2" t="n">
+        <v>4.128986913309739e+19</v>
+      </c>
+      <c r="CC2" t="n">
+        <v>7.500000000000002e+19</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Q3_Best</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>ddstartup_20251113_120706_parametric_lump</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>1.643433125582566e+16</v>
+      </c>
+      <c r="E3" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="F3" t="n">
+        <v>1801958069.217269</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0.005509706093257065</v>
+      </c>
+      <c r="H3" t="n">
+        <v>1.604044400954149</v>
+      </c>
+      <c r="I3" t="n">
+        <v>1</v>
+      </c>
+      <c r="J3" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="K3" t="n">
+        <v>10</v>
+      </c>
+      <c r="L3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="M3" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>b''</t>
+        </is>
+      </c>
+      <c r="O3" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="P3" t="n">
+        <v>2171636</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>6503081735241510</v>
+      </c>
+      <c r="R3" t="n">
+        <v>1.5e+20</v>
+      </c>
+      <c r="S3" t="n">
+        <v>9.722222222222221e-08</v>
+      </c>
+      <c r="T3" t="b">
+        <v>1</v>
+      </c>
+      <c r="U3" t="n">
+        <v>23015483.85849505</v>
+      </c>
+      <c r="V3" t="inlineStr"/>
+      <c r="W3" t="inlineStr"/>
+      <c r="X3" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>1597782205.427494</v>
       </c>
       <c r="AA3" t="inlineStr"/>
       <c r="AB3" t="inlineStr"/>
@@ -15562,49 +16431,49 @@
         <v>4375147.554038037</v>
       </c>
       <c r="AZ3" t="n">
-        <v>476233.9426265357</v>
+        <v>161426.9314990294</v>
       </c>
       <c r="BA3" t="n">
-        <v>476233.9426265357</v>
+        <v>161426.9314990294</v>
       </c>
       <c r="BB3" t="n">
-        <v>476233.9426265357</v>
+        <v>161426.9314990294</v>
       </c>
       <c r="BC3" t="n">
-        <v>476233.9426265357</v>
+        <v>161426.9314990294</v>
       </c>
       <c r="BD3" t="n">
-        <v>476233.9426265357</v>
+        <v>161426.9314990294</v>
       </c>
       <c r="BE3" t="n">
-        <v>516441161.9396554</v>
+        <v>1477808714.292928</v>
       </c>
       <c r="BF3" t="n">
-        <v>516441161.9396554</v>
+        <v>1477808714.292928</v>
       </c>
       <c r="BG3" t="n">
-        <v>516441161.9396554</v>
+        <v>1477808714.292928</v>
       </c>
       <c r="BH3" t="n">
-        <v>516441161.9396554</v>
+        <v>1477808714.292928</v>
       </c>
       <c r="BI3" t="n">
-        <v>516441161.9396554</v>
+        <v>1477808714.292928</v>
       </c>
       <c r="BJ3" t="n">
-        <v>162076158.2847663</v>
+        <v>1123384158.284766</v>
       </c>
       <c r="BK3" t="n">
-        <v>162076158.2847663</v>
+        <v>1123384158.284766</v>
       </c>
       <c r="BL3" t="n">
-        <v>162076158.2847663</v>
+        <v>1123384158.284766</v>
       </c>
       <c r="BM3" t="n">
-        <v>162076158.2847663</v>
+        <v>1123384158.284766</v>
       </c>
       <c r="BN3" t="n">
-        <v>162076158.2847663</v>
+        <v>1123384158.284766</v>
       </c>
       <c r="BO3" t="inlineStr"/>
       <c r="BP3" t="inlineStr"/>
@@ -15627,875 +16496,6 @@
         <v>1.5e+20</v>
       </c>
       <c r="BY3" t="n">
-        <v>9910759386455950</v>
-      </c>
-      <c r="BZ3" t="n">
-        <v>9910759386455950</v>
-      </c>
-      <c r="CA3" t="n">
-        <v>9910759386455950</v>
-      </c>
-      <c r="CB3" t="n">
-        <v>9910759386455950</v>
-      </c>
-      <c r="CC3" t="n">
-        <v>9910759386455950</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:CC3"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Strategy</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Rank_in_Strategy</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Source_File</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>E_lost</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>I_target</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>P_DT_eq</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>Q_DD</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>Q_DT_eq</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>TBR_DDn</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>TBR_DT</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>T_i</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>V_plasma</t>
-        </is>
-      </c>
-      <c r="M1" s="1" t="inlineStr">
-        <is>
-          <t>capacity_factor</t>
-        </is>
-      </c>
-      <c r="N1" s="1" t="inlineStr">
-        <is>
-          <t>error</t>
-        </is>
-      </c>
-      <c r="O1" s="1" t="inlineStr">
-        <is>
-          <t>eta_th</t>
-        </is>
-      </c>
-      <c r="P1" s="1" t="inlineStr">
-        <is>
-          <t>linear_index</t>
-        </is>
-      </c>
-      <c r="Q1" s="1" t="inlineStr">
-        <is>
-          <t>n_He3</t>
-        </is>
-      </c>
-      <c r="R1" s="1" t="inlineStr">
-        <is>
-          <t>n_tot</t>
-        </is>
-      </c>
-      <c r="S1" s="1" t="inlineStr">
-        <is>
-          <t>price_of_electricity</t>
-        </is>
-      </c>
-      <c r="T1" s="1" t="inlineStr">
-        <is>
-          <t>sol_success</t>
-        </is>
-      </c>
-      <c r="U1" s="1" t="inlineStr">
-        <is>
-          <t>t_startup</t>
-        </is>
-      </c>
-      <c r="V1" s="1" t="inlineStr">
-        <is>
-          <t>tau_ifc</t>
-        </is>
-      </c>
-      <c r="W1" s="1" t="inlineStr">
-        <is>
-          <t>tau_ofc</t>
-        </is>
-      </c>
-      <c r="X1" s="1" t="inlineStr">
-        <is>
-          <t>tau_p_He3</t>
-        </is>
-      </c>
-      <c r="Y1" s="1" t="inlineStr">
-        <is>
-          <t>tau_p_T</t>
-        </is>
-      </c>
-      <c r="Z1" s="1" t="inlineStr">
-        <is>
-          <t>unrealized_profits</t>
-        </is>
-      </c>
-      <c r="AA1" s="1" t="inlineStr">
-        <is>
-          <t>N_ifc_t0</t>
-        </is>
-      </c>
-      <c r="AB1" s="1" t="inlineStr">
-        <is>
-          <t>N_ifc_t25</t>
-        </is>
-      </c>
-      <c r="AC1" s="1" t="inlineStr">
-        <is>
-          <t>N_ifc_t50</t>
-        </is>
-      </c>
-      <c r="AD1" s="1" t="inlineStr">
-        <is>
-          <t>N_ifc_t75</t>
-        </is>
-      </c>
-      <c r="AE1" s="1" t="inlineStr">
-        <is>
-          <t>N_ifc_t100</t>
-        </is>
-      </c>
-      <c r="AF1" s="1" t="inlineStr">
-        <is>
-          <t>N_ofc_t0</t>
-        </is>
-      </c>
-      <c r="AG1" s="1" t="inlineStr">
-        <is>
-          <t>N_ofc_t25</t>
-        </is>
-      </c>
-      <c r="AH1" s="1" t="inlineStr">
-        <is>
-          <t>N_ofc_t50</t>
-        </is>
-      </c>
-      <c r="AI1" s="1" t="inlineStr">
-        <is>
-          <t>N_ofc_t75</t>
-        </is>
-      </c>
-      <c r="AJ1" s="1" t="inlineStr">
-        <is>
-          <t>N_ofc_t100</t>
-        </is>
-      </c>
-      <c r="AK1" s="1" t="inlineStr">
-        <is>
-          <t>N_stor_t0</t>
-        </is>
-      </c>
-      <c r="AL1" s="1" t="inlineStr">
-        <is>
-          <t>N_stor_t25</t>
-        </is>
-      </c>
-      <c r="AM1" s="1" t="inlineStr">
-        <is>
-          <t>N_stor_t50</t>
-        </is>
-      </c>
-      <c r="AN1" s="1" t="inlineStr">
-        <is>
-          <t>N_stor_t75</t>
-        </is>
-      </c>
-      <c r="AO1" s="1" t="inlineStr">
-        <is>
-          <t>N_stor_t100</t>
-        </is>
-      </c>
-      <c r="AP1" s="1" t="inlineStr">
-        <is>
-          <t>P_DDn_t0</t>
-        </is>
-      </c>
-      <c r="AQ1" s="1" t="inlineStr">
-        <is>
-          <t>P_DDn_t25</t>
-        </is>
-      </c>
-      <c r="AR1" s="1" t="inlineStr">
-        <is>
-          <t>P_DDn_t50</t>
-        </is>
-      </c>
-      <c r="AS1" s="1" t="inlineStr">
-        <is>
-          <t>P_DDn_t75</t>
-        </is>
-      </c>
-      <c r="AT1" s="1" t="inlineStr">
-        <is>
-          <t>P_DDn_t100</t>
-        </is>
-      </c>
-      <c r="AU1" s="1" t="inlineStr">
-        <is>
-          <t>P_DDp_t0</t>
-        </is>
-      </c>
-      <c r="AV1" s="1" t="inlineStr">
-        <is>
-          <t>P_DDp_t25</t>
-        </is>
-      </c>
-      <c r="AW1" s="1" t="inlineStr">
-        <is>
-          <t>P_DDp_t50</t>
-        </is>
-      </c>
-      <c r="AX1" s="1" t="inlineStr">
-        <is>
-          <t>P_DDp_t75</t>
-        </is>
-      </c>
-      <c r="AY1" s="1" t="inlineStr">
-        <is>
-          <t>P_DDp_t100</t>
-        </is>
-      </c>
-      <c r="AZ1" s="1" t="inlineStr">
-        <is>
-          <t>P_DT_t0</t>
-        </is>
-      </c>
-      <c r="BA1" s="1" t="inlineStr">
-        <is>
-          <t>P_DT_t25</t>
-        </is>
-      </c>
-      <c r="BB1" s="1" t="inlineStr">
-        <is>
-          <t>P_DT_t50</t>
-        </is>
-      </c>
-      <c r="BC1" s="1" t="inlineStr">
-        <is>
-          <t>P_DT_t75</t>
-        </is>
-      </c>
-      <c r="BD1" s="1" t="inlineStr">
-        <is>
-          <t>P_DT_t100</t>
-        </is>
-      </c>
-      <c r="BE1" s="1" t="inlineStr">
-        <is>
-          <t>P_aux_t0</t>
-        </is>
-      </c>
-      <c r="BF1" s="1" t="inlineStr">
-        <is>
-          <t>P_aux_t25</t>
-        </is>
-      </c>
-      <c r="BG1" s="1" t="inlineStr">
-        <is>
-          <t>P_aux_t50</t>
-        </is>
-      </c>
-      <c r="BH1" s="1" t="inlineStr">
-        <is>
-          <t>P_aux_t75</t>
-        </is>
-      </c>
-      <c r="BI1" s="1" t="inlineStr">
-        <is>
-          <t>P_aux_t100</t>
-        </is>
-      </c>
-      <c r="BJ1" s="1" t="inlineStr">
-        <is>
-          <t>P_aux_DT_eq_t0</t>
-        </is>
-      </c>
-      <c r="BK1" s="1" t="inlineStr">
-        <is>
-          <t>P_aux_DT_eq_t25</t>
-        </is>
-      </c>
-      <c r="BL1" s="1" t="inlineStr">
-        <is>
-          <t>P_aux_DT_eq_t50</t>
-        </is>
-      </c>
-      <c r="BM1" s="1" t="inlineStr">
-        <is>
-          <t>P_aux_DT_eq_t75</t>
-        </is>
-      </c>
-      <c r="BN1" s="1" t="inlineStr">
-        <is>
-          <t>P_aux_DT_eq_t100</t>
-        </is>
-      </c>
-      <c r="BO1" s="1" t="inlineStr">
-        <is>
-          <t>TBE_t0</t>
-        </is>
-      </c>
-      <c r="BP1" s="1" t="inlineStr">
-        <is>
-          <t>TBE_t25</t>
-        </is>
-      </c>
-      <c r="BQ1" s="1" t="inlineStr">
-        <is>
-          <t>TBE_t50</t>
-        </is>
-      </c>
-      <c r="BR1" s="1" t="inlineStr">
-        <is>
-          <t>TBE_t75</t>
-        </is>
-      </c>
-      <c r="BS1" s="1" t="inlineStr">
-        <is>
-          <t>TBE_t100</t>
-        </is>
-      </c>
-      <c r="BT1" s="1" t="inlineStr">
-        <is>
-          <t>n_D_t0</t>
-        </is>
-      </c>
-      <c r="BU1" s="1" t="inlineStr">
-        <is>
-          <t>n_D_t25</t>
-        </is>
-      </c>
-      <c r="BV1" s="1" t="inlineStr">
-        <is>
-          <t>n_D_t50</t>
-        </is>
-      </c>
-      <c r="BW1" s="1" t="inlineStr">
-        <is>
-          <t>n_D_t75</t>
-        </is>
-      </c>
-      <c r="BX1" s="1" t="inlineStr">
-        <is>
-          <t>n_D_t100</t>
-        </is>
-      </c>
-      <c r="BY1" s="1" t="inlineStr">
-        <is>
-          <t>n_T_t0</t>
-        </is>
-      </c>
-      <c r="BZ1" s="1" t="inlineStr">
-        <is>
-          <t>n_T_t25</t>
-        </is>
-      </c>
-      <c r="CA1" s="1" t="inlineStr">
-        <is>
-          <t>n_T_t50</t>
-        </is>
-      </c>
-      <c r="CB1" s="1" t="inlineStr">
-        <is>
-          <t>n_T_t75</t>
-        </is>
-      </c>
-      <c r="CC1" s="1" t="inlineStr">
-        <is>
-          <t>n_T_t100</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>Q3_Best</t>
-        </is>
-      </c>
-      <c r="B2" t="n">
-        <v>1</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>ddstartup_20251113_002935_parametric_T_seeded</t>
-        </is>
-      </c>
-      <c r="D2" t="n">
-        <v>7826287446143086</v>
-      </c>
-      <c r="E2" t="inlineStr"/>
-      <c r="F2" t="n">
-        <v>3603916138.434538</v>
-      </c>
-      <c r="G2" t="n">
-        <v>5.127455749410214</v>
-      </c>
-      <c r="H2" t="inlineStr"/>
-      <c r="I2" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="J2" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="K2" t="n">
-        <v>10</v>
-      </c>
-      <c r="L2" t="n">
-        <v>2000</v>
-      </c>
-      <c r="M2" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>b''</t>
-        </is>
-      </c>
-      <c r="O2" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="P2" t="n">
-        <v>5295627</v>
-      </c>
-      <c r="Q2" t="inlineStr"/>
-      <c r="R2" t="n">
-        <v>1.5e+20</v>
-      </c>
-      <c r="S2" t="n">
-        <v>4.166666666666666e-08</v>
-      </c>
-      <c r="T2" t="b">
-        <v>1</v>
-      </c>
-      <c r="U2" t="n">
-        <v>8906643.306762496</v>
-      </c>
-      <c r="V2" t="n">
-        <v>28800</v>
-      </c>
-      <c r="W2" t="n">
-        <v>7200</v>
-      </c>
-      <c r="X2" t="inlineStr"/>
-      <c r="Y2" t="n">
-        <v>5</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>326095310.2559619</v>
-      </c>
-      <c r="AA2" t="n">
-        <v>100</v>
-      </c>
-      <c r="AB2" t="n">
-        <v>6.891318357029416e+25</v>
-      </c>
-      <c r="AC2" t="n">
-        <v>2.194711298264947e+26</v>
-      </c>
-      <c r="AD2" t="n">
-        <v>5.048147762371376e+26</v>
-      </c>
-      <c r="AE2" t="n">
-        <v>9.007116213336876e+26</v>
-      </c>
-      <c r="AF2" t="n">
-        <v>100</v>
-      </c>
-      <c r="AG2" t="n">
-        <v>1.546425121460363e+24</v>
-      </c>
-      <c r="AH2" t="n">
-        <v>4.438176094912333e+24</v>
-      </c>
-      <c r="AI2" t="n">
-        <v>8.453174156956428e+24</v>
-      </c>
-      <c r="AJ2" t="n">
-        <v>1.059389795306354e+25</v>
-      </c>
-      <c r="AK2" t="n">
-        <v>100</v>
-      </c>
-      <c r="AL2" t="n">
-        <v>1.996731041002841e+23</v>
-      </c>
-      <c r="AM2" t="n">
-        <v>1.996731041002841e+23</v>
-      </c>
-      <c r="AN2" t="n">
-        <v>1.996731041002841e+23</v>
-      </c>
-      <c r="AO2" t="n">
-        <v>1.99697192644861e+23</v>
-      </c>
-      <c r="AP2" t="n">
-        <v>7210237.173850519</v>
-      </c>
-      <c r="AQ2" t="n">
-        <v>6685847.562828113</v>
-      </c>
-      <c r="AR2" t="n">
-        <v>5605200.967600255</v>
-      </c>
-      <c r="AS2" t="n">
-        <v>3787102.586796727</v>
-      </c>
-      <c r="AT2" t="n">
-        <v>1802559.293462631</v>
-      </c>
-      <c r="AU2" t="n">
-        <v>8750295.108076064</v>
-      </c>
-      <c r="AV2" t="n">
-        <v>8113899.419915252</v>
-      </c>
-      <c r="AW2" t="n">
-        <v>6802434.014855414</v>
-      </c>
-      <c r="AX2" t="n">
-        <v>4596002.106451184</v>
-      </c>
-      <c r="AY2" t="n">
-        <v>2187573.777019018</v>
-      </c>
-      <c r="AZ2" t="n">
-        <v>9.610443035825428e-06</v>
-      </c>
-      <c r="BA2" t="n">
-        <v>514320168.3826579</v>
-      </c>
-      <c r="BB2" t="n">
-        <v>1503627967.795042</v>
-      </c>
-      <c r="BC2" t="n">
-        <v>2875846322.130662</v>
-      </c>
-      <c r="BD2" t="n">
-        <v>3603916138.434538</v>
-      </c>
-      <c r="BE2" t="n">
-        <v>360081764.4814911</v>
-      </c>
-      <c r="BF2" t="n">
-        <v>359534221.9847848</v>
-      </c>
-      <c r="BG2" t="n">
-        <v>359489793.3288961</v>
-      </c>
-      <c r="BH2" t="n">
-        <v>358947823.0921111</v>
-      </c>
-      <c r="BI2" t="n">
-        <v>0</v>
-      </c>
-      <c r="BJ2" t="n">
-        <v>0</v>
-      </c>
-      <c r="BK2" t="n">
-        <v>0</v>
-      </c>
-      <c r="BL2" t="n">
-        <v>0</v>
-      </c>
-      <c r="BM2" t="n">
-        <v>0</v>
-      </c>
-      <c r="BN2" t="n">
-        <v>0</v>
-      </c>
-      <c r="BO2" t="inlineStr"/>
-      <c r="BP2" t="n">
-        <v>3.811278954004925e-05</v>
-      </c>
-      <c r="BQ2" t="n">
-        <v>3.498665693746704e-05</v>
-      </c>
-      <c r="BR2" t="n">
-        <v>2.909196494747936e-05</v>
-      </c>
-      <c r="BS2" t="n">
-        <v>2.043284501928585e-05</v>
-      </c>
-      <c r="BT2" t="n">
-        <v>1.499999999999999e+20</v>
-      </c>
-      <c r="BU2" t="n">
-        <v>1.444424076740985e+20</v>
-      </c>
-      <c r="BV2" t="n">
-        <v>1.322549933103414e+20</v>
-      </c>
-      <c r="BW2" t="n">
-        <v>1.087101308669026e+20</v>
-      </c>
-      <c r="BX2" t="n">
-        <v>7.499999999999998e+19</v>
-      </c>
-      <c r="BY2" t="n">
-        <v>100000</v>
-      </c>
-      <c r="BZ2" t="n">
-        <v>5.557592325901557e+18</v>
-      </c>
-      <c r="CA2" t="n">
-        <v>1.774500668965863e+19</v>
-      </c>
-      <c r="CB2" t="n">
-        <v>4.128986913309739e+19</v>
-      </c>
-      <c r="CC2" t="n">
-        <v>7.500000000000002e+19</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Q3_Best</t>
-        </is>
-      </c>
-      <c r="B3" t="n">
-        <v>1</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>ddstartup_20251113_120706_parametric_lump</t>
-        </is>
-      </c>
-      <c r="D3" t="n">
-        <v>1.643433125582566e+16</v>
-      </c>
-      <c r="E3" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="F3" t="n">
-        <v>1801958069.217269</v>
-      </c>
-      <c r="G3" t="n">
-        <v>0.005509706093257065</v>
-      </c>
-      <c r="H3" t="n">
-        <v>1.604044400954149</v>
-      </c>
-      <c r="I3" t="n">
-        <v>1</v>
-      </c>
-      <c r="J3" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="K3" t="n">
-        <v>10</v>
-      </c>
-      <c r="L3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="M3" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>b''</t>
-        </is>
-      </c>
-      <c r="O3" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="P3" t="n">
-        <v>2171636</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>6503081735241510</v>
-      </c>
-      <c r="R3" t="n">
-        <v>1.5e+20</v>
-      </c>
-      <c r="S3" t="n">
-        <v>9.722222222222221e-08</v>
-      </c>
-      <c r="T3" t="b">
-        <v>1</v>
-      </c>
-      <c r="U3" t="n">
-        <v>23015483.85849505</v>
-      </c>
-      <c r="V3" t="inlineStr"/>
-      <c r="W3" t="inlineStr"/>
-      <c r="X3" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y3" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>1597782205.427494</v>
-      </c>
-      <c r="AA3" t="inlineStr"/>
-      <c r="AB3" t="inlineStr"/>
-      <c r="AC3" t="inlineStr"/>
-      <c r="AD3" t="inlineStr"/>
-      <c r="AE3" t="inlineStr"/>
-      <c r="AF3" t="inlineStr"/>
-      <c r="AG3" t="inlineStr"/>
-      <c r="AH3" t="inlineStr"/>
-      <c r="AI3" t="inlineStr"/>
-      <c r="AJ3" t="inlineStr"/>
-      <c r="AK3" t="inlineStr"/>
-      <c r="AL3" t="inlineStr"/>
-      <c r="AM3" t="inlineStr"/>
-      <c r="AN3" t="inlineStr"/>
-      <c r="AO3" t="inlineStr"/>
-      <c r="AP3" t="n">
-        <v>3605118.586925264</v>
-      </c>
-      <c r="AQ3" t="n">
-        <v>3605118.586925264</v>
-      </c>
-      <c r="AR3" t="n">
-        <v>3605118.586925264</v>
-      </c>
-      <c r="AS3" t="n">
-        <v>3605118.586925264</v>
-      </c>
-      <c r="AT3" t="n">
-        <v>3605118.586925264</v>
-      </c>
-      <c r="AU3" t="n">
-        <v>4375147.554038037</v>
-      </c>
-      <c r="AV3" t="n">
-        <v>4375147.554038037</v>
-      </c>
-      <c r="AW3" t="n">
-        <v>4375147.554038037</v>
-      </c>
-      <c r="AX3" t="n">
-        <v>4375147.554038037</v>
-      </c>
-      <c r="AY3" t="n">
-        <v>4375147.554038037</v>
-      </c>
-      <c r="AZ3" t="n">
-        <v>161426.9314990294</v>
-      </c>
-      <c r="BA3" t="n">
-        <v>161426.9314990294</v>
-      </c>
-      <c r="BB3" t="n">
-        <v>161426.9314990294</v>
-      </c>
-      <c r="BC3" t="n">
-        <v>161426.9314990294</v>
-      </c>
-      <c r="BD3" t="n">
-        <v>161426.9314990294</v>
-      </c>
-      <c r="BE3" t="n">
-        <v>1477808714.292928</v>
-      </c>
-      <c r="BF3" t="n">
-        <v>1477808714.292928</v>
-      </c>
-      <c r="BG3" t="n">
-        <v>1477808714.292928</v>
-      </c>
-      <c r="BH3" t="n">
-        <v>1477808714.292928</v>
-      </c>
-      <c r="BI3" t="n">
-        <v>1477808714.292928</v>
-      </c>
-      <c r="BJ3" t="n">
-        <v>1123384158.284766</v>
-      </c>
-      <c r="BK3" t="n">
-        <v>1123384158.284766</v>
-      </c>
-      <c r="BL3" t="n">
-        <v>1123384158.284766</v>
-      </c>
-      <c r="BM3" t="n">
-        <v>1123384158.284766</v>
-      </c>
-      <c r="BN3" t="n">
-        <v>1123384158.284766</v>
-      </c>
-      <c r="BO3" t="inlineStr"/>
-      <c r="BP3" t="inlineStr"/>
-      <c r="BQ3" t="inlineStr"/>
-      <c r="BR3" t="inlineStr"/>
-      <c r="BS3" t="inlineStr"/>
-      <c r="BT3" t="n">
-        <v>1.5e+20</v>
-      </c>
-      <c r="BU3" t="n">
-        <v>1.5e+20</v>
-      </c>
-      <c r="BV3" t="n">
-        <v>1.5e+20</v>
-      </c>
-      <c r="BW3" t="n">
-        <v>1.5e+20</v>
-      </c>
-      <c r="BX3" t="n">
-        <v>1.5e+20</v>
-      </c>
-      <c r="BY3" t="n">
         <v>3359406655806988</v>
       </c>
       <c r="BZ3" t="n">
